--- a/AAII_Financials/Quarterly/BAK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAK_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -794,25 +794,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3429000</v>
+        <v>3342100</v>
       </c>
       <c r="E8" s="3">
-        <v>3651200</v>
+        <v>3558700</v>
       </c>
       <c r="F8" s="3">
-        <v>3998700</v>
+        <v>3897400</v>
       </c>
       <c r="G8" s="3">
-        <v>3904900</v>
+        <v>3805900</v>
       </c>
       <c r="H8" s="3">
-        <v>5220300</v>
+        <v>5088000</v>
       </c>
       <c r="I8" s="3">
-        <v>5225300</v>
+        <v>5092900</v>
       </c>
       <c r="J8" s="3">
-        <v>5496800</v>
+        <v>5357500</v>
       </c>
       <c r="K8" s="3">
         <v>5694300</v>
@@ -886,25 +886,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3312000</v>
+        <v>3228000</v>
       </c>
       <c r="E9" s="3">
-        <v>3556900</v>
+        <v>3466800</v>
       </c>
       <c r="F9" s="3">
-        <v>3796200</v>
+        <v>3700000</v>
       </c>
       <c r="G9" s="3">
-        <v>3921000</v>
+        <v>3821600</v>
       </c>
       <c r="H9" s="3">
-        <v>4762000</v>
+        <v>4641400</v>
       </c>
       <c r="I9" s="3">
-        <v>4386700</v>
+        <v>4275500</v>
       </c>
       <c r="J9" s="3">
-        <v>4441900</v>
+        <v>4329400</v>
       </c>
       <c r="K9" s="3">
         <v>4341600</v>
@@ -978,25 +978,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>117000</v>
+        <v>114100</v>
       </c>
       <c r="E10" s="3">
-        <v>94300</v>
+        <v>91900</v>
       </c>
       <c r="F10" s="3">
-        <v>202500</v>
+        <v>197400</v>
       </c>
       <c r="G10" s="3">
-        <v>-16100</v>
+        <v>-15700</v>
       </c>
       <c r="H10" s="3">
-        <v>458300</v>
+        <v>446600</v>
       </c>
       <c r="I10" s="3">
-        <v>838700</v>
+        <v>817400</v>
       </c>
       <c r="J10" s="3">
-        <v>1054900</v>
+        <v>1028100</v>
       </c>
       <c r="K10" s="3">
         <v>1352700</v>
@@ -1104,25 +1104,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>18900</v>
+        <v>18500</v>
       </c>
       <c r="E12" s="3">
-        <v>16700</v>
+        <v>16300</v>
       </c>
       <c r="F12" s="3">
-        <v>19300</v>
+        <v>18800</v>
       </c>
       <c r="G12" s="3">
-        <v>24500</v>
+        <v>23900</v>
       </c>
       <c r="H12" s="3">
-        <v>21400</v>
+        <v>20900</v>
       </c>
       <c r="I12" s="3">
-        <v>16100</v>
+        <v>15700</v>
       </c>
       <c r="J12" s="3">
-        <v>15000</v>
+        <v>14600</v>
       </c>
       <c r="K12" s="3">
         <v>19900</v>
@@ -1291,22 +1291,22 @@
         <v>10</v>
       </c>
       <c r="E14" s="3">
-        <v>220600</v>
+        <v>215100</v>
       </c>
       <c r="F14" s="3">
-        <v>30200</v>
+        <v>29500</v>
       </c>
       <c r="G14" s="3">
-        <v>19300</v>
+        <v>18800</v>
       </c>
       <c r="H14" s="3">
-        <v>30400</v>
+        <v>29700</v>
       </c>
       <c r="I14" s="3">
-        <v>244300</v>
+        <v>238100</v>
       </c>
       <c r="J14" s="3">
-        <v>24500</v>
+        <v>23800</v>
       </c>
       <c r="K14" s="3">
         <v>332300</v>
@@ -1506,22 +1506,22 @@
         <v>10</v>
       </c>
       <c r="E17" s="3">
-        <v>3988500</v>
+        <v>3887400</v>
       </c>
       <c r="F17" s="3">
-        <v>3896700</v>
+        <v>3798000</v>
       </c>
       <c r="G17" s="3">
-        <v>4283900</v>
+        <v>4175300</v>
       </c>
       <c r="H17" s="3">
-        <v>5078300</v>
+        <v>4949700</v>
       </c>
       <c r="I17" s="3">
-        <v>4885100</v>
+        <v>4761300</v>
       </c>
       <c r="J17" s="3">
-        <v>4721500</v>
+        <v>4601900</v>
       </c>
       <c r="K17" s="3">
         <v>4943100</v>
@@ -1598,22 +1598,22 @@
         <v>10</v>
       </c>
       <c r="E18" s="3">
-        <v>-337300</v>
+        <v>-328700</v>
       </c>
       <c r="F18" s="3">
-        <v>102000</v>
+        <v>99400</v>
       </c>
       <c r="G18" s="3">
-        <v>-379000</v>
+        <v>-369400</v>
       </c>
       <c r="H18" s="3">
-        <v>141900</v>
+        <v>138300</v>
       </c>
       <c r="I18" s="3">
-        <v>340200</v>
+        <v>331600</v>
       </c>
       <c r="J18" s="3">
-        <v>775300</v>
+        <v>755600</v>
       </c>
       <c r="K18" s="3">
         <v>751200</v>
@@ -1724,22 +1724,22 @@
         <v>10</v>
       </c>
       <c r="E20" s="3">
-        <v>225300</v>
+        <v>219600</v>
       </c>
       <c r="F20" s="3">
-        <v>144000</v>
+        <v>140300</v>
       </c>
       <c r="G20" s="3">
-        <v>104500</v>
+        <v>101800</v>
       </c>
       <c r="H20" s="3">
-        <v>-165000</v>
+        <v>-160900</v>
       </c>
       <c r="I20" s="3">
-        <v>-521200</v>
+        <v>-508000</v>
       </c>
       <c r="J20" s="3">
-        <v>397400</v>
+        <v>387400</v>
       </c>
       <c r="K20" s="3">
         <v>-334000</v>
@@ -1816,22 +1816,22 @@
         <v>10</v>
       </c>
       <c r="E21" s="3">
-        <v>156200</v>
+        <v>152300</v>
       </c>
       <c r="F21" s="3">
-        <v>499000</v>
+        <v>486400</v>
       </c>
       <c r="G21" s="3">
-        <v>19800</v>
+        <v>19300</v>
       </c>
       <c r="H21" s="3">
-        <v>218800</v>
+        <v>213300</v>
       </c>
       <c r="I21" s="3">
-        <v>48500</v>
+        <v>47200</v>
       </c>
       <c r="J21" s="3">
-        <v>1380400</v>
+        <v>1345400</v>
       </c>
       <c r="K21" s="3">
         <v>692900</v>
@@ -1908,22 +1908,22 @@
         <v>10</v>
       </c>
       <c r="E22" s="3">
-        <v>192300</v>
+        <v>187400</v>
       </c>
       <c r="F22" s="3">
-        <v>216300</v>
+        <v>210900</v>
       </c>
       <c r="G22" s="3">
-        <v>183400</v>
+        <v>178800</v>
       </c>
       <c r="H22" s="3">
-        <v>183600</v>
+        <v>179000</v>
       </c>
       <c r="I22" s="3">
-        <v>176500</v>
+        <v>172000</v>
       </c>
       <c r="J22" s="3">
-        <v>140900</v>
+        <v>137300</v>
       </c>
       <c r="K22" s="3">
         <v>165300</v>
@@ -1997,25 +1997,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-623100</v>
+        <v>-607300</v>
       </c>
       <c r="E23" s="3">
-        <v>-304200</v>
+        <v>-296500</v>
       </c>
       <c r="F23" s="3">
-        <v>29600</v>
+        <v>28900</v>
       </c>
       <c r="G23" s="3">
-        <v>-457900</v>
+        <v>-446300</v>
       </c>
       <c r="H23" s="3">
-        <v>-206700</v>
+        <v>-201500</v>
       </c>
       <c r="I23" s="3">
-        <v>-357400</v>
+        <v>-348300</v>
       </c>
       <c r="J23" s="3">
-        <v>1031800</v>
+        <v>1005600</v>
       </c>
       <c r="K23" s="3">
         <v>251900</v>
@@ -2089,25 +2089,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-97100</v>
+        <v>-94600</v>
       </c>
       <c r="E24" s="3">
-        <v>-134900</v>
+        <v>-131500</v>
       </c>
       <c r="F24" s="3">
-        <v>-20200</v>
+        <v>-19700</v>
       </c>
       <c r="G24" s="3">
-        <v>-70700</v>
+        <v>-68900</v>
       </c>
       <c r="H24" s="3">
-        <v>85600</v>
+        <v>83500</v>
       </c>
       <c r="I24" s="3">
-        <v>-56600</v>
+        <v>-55200</v>
       </c>
       <c r="J24" s="3">
-        <v>220100</v>
+        <v>214500</v>
       </c>
       <c r="K24" s="3">
         <v>157400</v>
@@ -2273,25 +2273,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-526000</v>
+        <v>-512700</v>
       </c>
       <c r="E26" s="3">
-        <v>-169300</v>
+        <v>-165000</v>
       </c>
       <c r="F26" s="3">
-        <v>49900</v>
+        <v>48600</v>
       </c>
       <c r="G26" s="3">
-        <v>-387300</v>
+        <v>-377400</v>
       </c>
       <c r="H26" s="3">
-        <v>-292400</v>
+        <v>-285000</v>
       </c>
       <c r="I26" s="3">
-        <v>-300800</v>
+        <v>-293200</v>
       </c>
       <c r="J26" s="3">
-        <v>811700</v>
+        <v>791100</v>
       </c>
       <c r="K26" s="3">
         <v>94500</v>
@@ -2365,25 +2365,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-497300</v>
+        <v>-484700</v>
       </c>
       <c r="E27" s="3">
-        <v>-158500</v>
+        <v>-154400</v>
       </c>
       <c r="F27" s="3">
-        <v>37900</v>
+        <v>37000</v>
       </c>
       <c r="G27" s="3">
-        <v>-351700</v>
+        <v>-342800</v>
       </c>
       <c r="H27" s="3">
-        <v>-226800</v>
+        <v>-221100</v>
       </c>
       <c r="I27" s="3">
-        <v>-289100</v>
+        <v>-281800</v>
       </c>
       <c r="J27" s="3">
-        <v>798600</v>
+        <v>778400</v>
       </c>
       <c r="K27" s="3">
         <v>107000</v>
@@ -2828,22 +2828,22 @@
         <v>10</v>
       </c>
       <c r="E32" s="3">
-        <v>-225300</v>
+        <v>-219600</v>
       </c>
       <c r="F32" s="3">
-        <v>-144000</v>
+        <v>-140300</v>
       </c>
       <c r="G32" s="3">
-        <v>-104500</v>
+        <v>-101800</v>
       </c>
       <c r="H32" s="3">
-        <v>165000</v>
+        <v>160900</v>
       </c>
       <c r="I32" s="3">
-        <v>521200</v>
+        <v>508000</v>
       </c>
       <c r="J32" s="3">
-        <v>-397400</v>
+        <v>-387400</v>
       </c>
       <c r="K32" s="3">
         <v>334000</v>
@@ -2917,25 +2917,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-497300</v>
+        <v>-484700</v>
       </c>
       <c r="E33" s="3">
-        <v>-158500</v>
+        <v>-154400</v>
       </c>
       <c r="F33" s="3">
-        <v>37900</v>
+        <v>37000</v>
       </c>
       <c r="G33" s="3">
-        <v>-351700</v>
+        <v>-342800</v>
       </c>
       <c r="H33" s="3">
-        <v>-226800</v>
+        <v>-221100</v>
       </c>
       <c r="I33" s="3">
-        <v>-289100</v>
+        <v>-281800</v>
       </c>
       <c r="J33" s="3">
-        <v>798600</v>
+        <v>778400</v>
       </c>
       <c r="K33" s="3">
         <v>107000</v>
@@ -3101,25 +3101,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-497300</v>
+        <v>-484700</v>
       </c>
       <c r="E35" s="3">
-        <v>-158500</v>
+        <v>-154400</v>
       </c>
       <c r="F35" s="3">
-        <v>37900</v>
+        <v>37000</v>
       </c>
       <c r="G35" s="3">
-        <v>-351700</v>
+        <v>-342800</v>
       </c>
       <c r="H35" s="3">
-        <v>-226800</v>
+        <v>-221100</v>
       </c>
       <c r="I35" s="3">
-        <v>-289100</v>
+        <v>-281800</v>
       </c>
       <c r="J35" s="3">
-        <v>798600</v>
+        <v>778400</v>
       </c>
       <c r="K35" s="3">
         <v>107000</v>
@@ -3358,25 +3358,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2804100</v>
+        <v>2733100</v>
       </c>
       <c r="E41" s="3">
-        <v>2722600</v>
+        <v>2653600</v>
       </c>
       <c r="F41" s="3">
-        <v>2546400</v>
+        <v>2481800</v>
       </c>
       <c r="G41" s="3">
-        <v>2563500</v>
+        <v>2498500</v>
       </c>
       <c r="H41" s="3">
-        <v>2413500</v>
+        <v>2352400</v>
       </c>
       <c r="I41" s="3">
-        <v>1959200</v>
+        <v>1909600</v>
       </c>
       <c r="J41" s="3">
-        <v>2079900</v>
+        <v>2027200</v>
       </c>
       <c r="K41" s="3">
         <v>1752100</v>
@@ -3450,25 +3450,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1036900</v>
+        <v>1010600</v>
       </c>
       <c r="E42" s="3">
-        <v>481200</v>
+        <v>469000</v>
       </c>
       <c r="F42" s="3">
-        <v>787200</v>
+        <v>767300</v>
       </c>
       <c r="G42" s="3">
-        <v>472000</v>
+        <v>460100</v>
       </c>
       <c r="H42" s="3">
-        <v>512400</v>
+        <v>499400</v>
       </c>
       <c r="I42" s="3">
-        <v>786600</v>
+        <v>766700</v>
       </c>
       <c r="J42" s="3">
-        <v>426800</v>
+        <v>416000</v>
       </c>
       <c r="K42" s="3">
         <v>705000</v>
@@ -3542,25 +3542,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1225300</v>
+        <v>1194200</v>
       </c>
       <c r="E43" s="3">
-        <v>1131900</v>
+        <v>1103300</v>
       </c>
       <c r="F43" s="3">
-        <v>1330500</v>
+        <v>1296800</v>
       </c>
       <c r="G43" s="3">
-        <v>1132600</v>
+        <v>1103900</v>
       </c>
       <c r="H43" s="3">
-        <v>1877900</v>
+        <v>1830300</v>
       </c>
       <c r="I43" s="3">
-        <v>1938100</v>
+        <v>1889000</v>
       </c>
       <c r="J43" s="3">
-        <v>2030400</v>
+        <v>1979000</v>
       </c>
       <c r="K43" s="3">
         <v>2082100</v>
@@ -3634,25 +3634,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2565400</v>
+        <v>2500400</v>
       </c>
       <c r="E44" s="3">
-        <v>2670000</v>
+        <v>2602400</v>
       </c>
       <c r="F44" s="3">
-        <v>2833900</v>
+        <v>2762100</v>
       </c>
       <c r="G44" s="3">
-        <v>2885000</v>
+        <v>2811900</v>
       </c>
       <c r="H44" s="3">
-        <v>3087200</v>
+        <v>3009000</v>
       </c>
       <c r="I44" s="3">
-        <v>3500400</v>
+        <v>3411700</v>
       </c>
       <c r="J44" s="3">
-        <v>3485100</v>
+        <v>3396800</v>
       </c>
       <c r="K44" s="3">
         <v>3297100</v>
@@ -3726,25 +3726,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>33300</v>
+        <v>32400</v>
       </c>
       <c r="E45" s="3">
-        <v>55400</v>
+        <v>54000</v>
       </c>
       <c r="F45" s="3">
-        <v>35600</v>
+        <v>34700</v>
       </c>
       <c r="G45" s="3">
-        <v>32500</v>
+        <v>31600</v>
       </c>
       <c r="H45" s="3">
-        <v>11500</v>
+        <v>11300</v>
       </c>
       <c r="I45" s="3">
-        <v>19000</v>
+        <v>18500</v>
       </c>
       <c r="J45" s="3">
-        <v>153200</v>
+        <v>149300</v>
       </c>
       <c r="K45" s="3">
         <v>94700</v>
@@ -3818,25 +3818,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7665000</v>
+        <v>7470800</v>
       </c>
       <c r="E46" s="3">
-        <v>7061100</v>
+        <v>6882200</v>
       </c>
       <c r="F46" s="3">
-        <v>7533600</v>
+        <v>7342700</v>
       </c>
       <c r="G46" s="3">
-        <v>7085500</v>
+        <v>6906000</v>
       </c>
       <c r="H46" s="3">
-        <v>7902600</v>
+        <v>7702400</v>
       </c>
       <c r="I46" s="3">
-        <v>8203300</v>
+        <v>7995400</v>
       </c>
       <c r="J46" s="3">
-        <v>8175400</v>
+        <v>7968300</v>
       </c>
       <c r="K46" s="3">
         <v>7931000</v>
@@ -3910,25 +3910,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1516900</v>
+        <v>1478500</v>
       </c>
       <c r="E47" s="3">
-        <v>481200</v>
+        <v>469000</v>
       </c>
       <c r="F47" s="3">
-        <v>478700</v>
+        <v>466600</v>
       </c>
       <c r="G47" s="3">
-        <v>453900</v>
+        <v>442400</v>
       </c>
       <c r="H47" s="3">
-        <v>484700</v>
+        <v>472400</v>
       </c>
       <c r="I47" s="3">
-        <v>449600</v>
+        <v>438300</v>
       </c>
       <c r="J47" s="3">
-        <v>386200</v>
+        <v>376400</v>
       </c>
       <c r="K47" s="3">
         <v>391000</v>
@@ -4002,25 +4002,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>8660800</v>
+        <v>8441400</v>
       </c>
       <c r="E48" s="3">
-        <v>8552300</v>
+        <v>8335600</v>
       </c>
       <c r="F48" s="3">
-        <v>8662300</v>
+        <v>8442800</v>
       </c>
       <c r="G48" s="3">
-        <v>8578100</v>
+        <v>8360800</v>
       </c>
       <c r="H48" s="3">
-        <v>8454100</v>
+        <v>8239900</v>
       </c>
       <c r="I48" s="3">
-        <v>8103400</v>
+        <v>7898100</v>
       </c>
       <c r="J48" s="3">
-        <v>7535500</v>
+        <v>7344600</v>
       </c>
       <c r="K48" s="3">
         <v>8074600</v>
@@ -4094,25 +4094,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>638900</v>
+        <v>622700</v>
       </c>
       <c r="E49" s="3">
-        <v>633100</v>
+        <v>617000</v>
       </c>
       <c r="F49" s="3">
-        <v>634200</v>
+        <v>618100</v>
       </c>
       <c r="G49" s="3">
-        <v>621400</v>
+        <v>605700</v>
       </c>
       <c r="H49" s="3">
-        <v>605400</v>
+        <v>590000</v>
       </c>
       <c r="I49" s="3">
-        <v>586300</v>
+        <v>571400</v>
       </c>
       <c r="J49" s="3">
-        <v>580100</v>
+        <v>565400</v>
       </c>
       <c r="K49" s="3">
         <v>580800</v>
@@ -4370,25 +4370,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>82200</v>
+        <v>80100</v>
       </c>
       <c r="E52" s="3">
-        <v>1369600</v>
+        <v>1334900</v>
       </c>
       <c r="F52" s="3">
-        <v>1290400</v>
+        <v>1257700</v>
       </c>
       <c r="G52" s="3">
-        <v>1366500</v>
+        <v>1331900</v>
       </c>
       <c r="H52" s="3">
-        <v>1514200</v>
+        <v>1475900</v>
       </c>
       <c r="I52" s="3">
-        <v>1528000</v>
+        <v>1489300</v>
       </c>
       <c r="J52" s="3">
-        <v>1198500</v>
+        <v>1168100</v>
       </c>
       <c r="K52" s="3">
         <v>1705900</v>
@@ -4554,25 +4554,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>18921100</v>
+        <v>18441700</v>
       </c>
       <c r="E54" s="3">
-        <v>18097300</v>
+        <v>17638800</v>
       </c>
       <c r="F54" s="3">
-        <v>18599100</v>
+        <v>18127900</v>
       </c>
       <c r="G54" s="3">
-        <v>18105500</v>
+        <v>17646800</v>
       </c>
       <c r="H54" s="3">
-        <v>18960900</v>
+        <v>18480500</v>
       </c>
       <c r="I54" s="3">
-        <v>18870500</v>
+        <v>18392400</v>
       </c>
       <c r="J54" s="3">
-        <v>17875700</v>
+        <v>17422800</v>
       </c>
       <c r="K54" s="3">
         <v>18683200</v>
@@ -4714,25 +4714,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2730300</v>
+        <v>2661200</v>
       </c>
       <c r="E57" s="3">
-        <v>2460000</v>
+        <v>2397700</v>
       </c>
       <c r="F57" s="3">
-        <v>2517600</v>
+        <v>2453800</v>
       </c>
       <c r="G57" s="3">
-        <v>2518300</v>
+        <v>2454500</v>
       </c>
       <c r="H57" s="3">
-        <v>2644200</v>
+        <v>2577200</v>
       </c>
       <c r="I57" s="3">
-        <v>2613900</v>
+        <v>2547700</v>
       </c>
       <c r="J57" s="3">
-        <v>2478600</v>
+        <v>2415800</v>
       </c>
       <c r="K57" s="3">
         <v>2432800</v>
@@ -4806,25 +4806,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>691500</v>
+        <v>673900</v>
       </c>
       <c r="E58" s="3">
-        <v>720800</v>
+        <v>702600</v>
       </c>
       <c r="F58" s="3">
-        <v>686400</v>
+        <v>669000</v>
       </c>
       <c r="G58" s="3">
-        <v>676700</v>
+        <v>659500</v>
       </c>
       <c r="H58" s="3">
-        <v>521000</v>
+        <v>507800</v>
       </c>
       <c r="I58" s="3">
-        <v>547700</v>
+        <v>533800</v>
       </c>
       <c r="J58" s="3">
-        <v>630700</v>
+        <v>614800</v>
       </c>
       <c r="K58" s="3">
         <v>436900</v>
@@ -4898,25 +4898,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1550400</v>
+        <v>1511100</v>
       </c>
       <c r="E59" s="3">
-        <v>1571700</v>
+        <v>1531900</v>
       </c>
       <c r="F59" s="3">
-        <v>1742900</v>
+        <v>1698700</v>
       </c>
       <c r="G59" s="3">
-        <v>1778200</v>
+        <v>1733200</v>
       </c>
       <c r="H59" s="3">
-        <v>1994300</v>
+        <v>1943800</v>
       </c>
       <c r="I59" s="3">
-        <v>2121800</v>
+        <v>2068000</v>
       </c>
       <c r="J59" s="3">
-        <v>1901800</v>
+        <v>1853600</v>
       </c>
       <c r="K59" s="3">
         <v>2215300</v>
@@ -4990,25 +4990,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4972200</v>
+        <v>4846200</v>
       </c>
       <c r="E60" s="3">
-        <v>4752600</v>
+        <v>4632100</v>
       </c>
       <c r="F60" s="3">
-        <v>4946900</v>
+        <v>4821500</v>
       </c>
       <c r="G60" s="3">
-        <v>4973200</v>
+        <v>4847200</v>
       </c>
       <c r="H60" s="3">
-        <v>5159600</v>
+        <v>5028800</v>
       </c>
       <c r="I60" s="3">
-        <v>5283400</v>
+        <v>5149500</v>
       </c>
       <c r="J60" s="3">
-        <v>5011100</v>
+        <v>4884200</v>
       </c>
       <c r="K60" s="3">
         <v>5085100</v>
@@ -5082,25 +5082,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11121100</v>
+        <v>10839300</v>
       </c>
       <c r="E61" s="3">
-        <v>9917400</v>
+        <v>9666200</v>
       </c>
       <c r="F61" s="3">
-        <v>10363100</v>
+        <v>10100600</v>
       </c>
       <c r="G61" s="3">
-        <v>9877800</v>
+        <v>9627600</v>
       </c>
       <c r="H61" s="3">
-        <v>10157500</v>
+        <v>9900200</v>
       </c>
       <c r="I61" s="3">
-        <v>9591200</v>
+        <v>9348200</v>
       </c>
       <c r="J61" s="3">
-        <v>8475600</v>
+        <v>8260900</v>
       </c>
       <c r="K61" s="3">
         <v>9768500</v>
@@ -5174,25 +5174,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4658000</v>
+        <v>4539900</v>
       </c>
       <c r="E62" s="3">
-        <v>2040800</v>
+        <v>1989100</v>
       </c>
       <c r="F62" s="3">
-        <v>1818300</v>
+        <v>1772200</v>
       </c>
       <c r="G62" s="3">
-        <v>1998400</v>
+        <v>1947800</v>
       </c>
       <c r="H62" s="3">
-        <v>2239600</v>
+        <v>2182800</v>
       </c>
       <c r="I62" s="3">
-        <v>2353400</v>
+        <v>2293800</v>
       </c>
       <c r="J62" s="3">
-        <v>2273100</v>
+        <v>2215500</v>
       </c>
       <c r="K62" s="3">
         <v>2577400</v>
@@ -5542,25 +5542,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>17888300</v>
+        <v>17435100</v>
       </c>
       <c r="E66" s="3">
-        <v>16610100</v>
+        <v>16189300</v>
       </c>
       <c r="F66" s="3">
-        <v>16989700</v>
+        <v>16559200</v>
       </c>
       <c r="G66" s="3">
-        <v>16599900</v>
+        <v>16179300</v>
       </c>
       <c r="H66" s="3">
-        <v>17174100</v>
+        <v>16739000</v>
       </c>
       <c r="I66" s="3">
-        <v>16923400</v>
+        <v>16494600</v>
       </c>
       <c r="J66" s="3">
-        <v>15490700</v>
+        <v>15098200</v>
       </c>
       <c r="K66" s="3">
         <v>17095600</v>
@@ -6036,25 +6036,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-239900</v>
+        <v>-233800</v>
       </c>
       <c r="E72" s="3">
-        <v>256800</v>
+        <v>250300</v>
       </c>
       <c r="F72" s="3">
-        <v>416000</v>
+        <v>405400</v>
       </c>
       <c r="G72" s="3">
-        <v>376700</v>
+        <v>367100</v>
       </c>
       <c r="H72" s="3">
-        <v>726800</v>
+        <v>708400</v>
       </c>
       <c r="I72" s="3">
-        <v>952300</v>
+        <v>928100</v>
       </c>
       <c r="J72" s="3">
-        <v>1517100</v>
+        <v>1478700</v>
       </c>
       <c r="K72" s="3">
         <v>703900</v>
@@ -6404,25 +6404,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1032800</v>
+        <v>1006600</v>
       </c>
       <c r="E76" s="3">
-        <v>1487200</v>
+        <v>1449600</v>
       </c>
       <c r="F76" s="3">
-        <v>1609400</v>
+        <v>1568600</v>
       </c>
       <c r="G76" s="3">
-        <v>1505600</v>
+        <v>1467400</v>
       </c>
       <c r="H76" s="3">
-        <v>1786800</v>
+        <v>1741500</v>
       </c>
       <c r="I76" s="3">
-        <v>1947200</v>
+        <v>1897800</v>
       </c>
       <c r="J76" s="3">
-        <v>2385000</v>
+        <v>2324600</v>
       </c>
       <c r="K76" s="3">
         <v>1587600</v>
@@ -6685,25 +6685,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-497300</v>
+        <v>-484700</v>
       </c>
       <c r="E81" s="3">
-        <v>-158500</v>
+        <v>-154400</v>
       </c>
       <c r="F81" s="3">
-        <v>37900</v>
+        <v>37000</v>
       </c>
       <c r="G81" s="3">
-        <v>-351700</v>
+        <v>-342800</v>
       </c>
       <c r="H81" s="3">
-        <v>-226800</v>
+        <v>-221100</v>
       </c>
       <c r="I81" s="3">
-        <v>-289100</v>
+        <v>-281800</v>
       </c>
       <c r="J81" s="3">
-        <v>798600</v>
+        <v>778400</v>
       </c>
       <c r="K81" s="3">
         <v>107000</v>
@@ -6811,25 +6811,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>264300</v>
+        <v>257600</v>
       </c>
       <c r="E83" s="3">
-        <v>268200</v>
+        <v>261400</v>
       </c>
       <c r="F83" s="3">
-        <v>253000</v>
+        <v>246600</v>
       </c>
       <c r="G83" s="3">
-        <v>294300</v>
+        <v>286900</v>
       </c>
       <c r="H83" s="3">
-        <v>241900</v>
+        <v>235800</v>
       </c>
       <c r="I83" s="3">
-        <v>229400</v>
+        <v>223600</v>
       </c>
       <c r="J83" s="3">
-        <v>207700</v>
+        <v>202400</v>
       </c>
       <c r="K83" s="3">
         <v>275600</v>
@@ -7363,25 +7363,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-506600</v>
+        <v>-493700</v>
       </c>
       <c r="E89" s="3">
-        <v>407000</v>
+        <v>396700</v>
       </c>
       <c r="F89" s="3">
-        <v>-576100</v>
+        <v>-561500</v>
       </c>
       <c r="G89" s="3">
-        <v>475200</v>
+        <v>463100</v>
       </c>
       <c r="H89" s="3">
-        <v>603700</v>
+        <v>588400</v>
       </c>
       <c r="I89" s="3">
-        <v>410400</v>
+        <v>400000</v>
       </c>
       <c r="J89" s="3">
-        <v>351500</v>
+        <v>342600</v>
       </c>
       <c r="K89" s="3">
         <v>854400</v>
@@ -7765,25 +7765,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-251600</v>
+        <v>-245200</v>
       </c>
       <c r="E94" s="3">
-        <v>-178600</v>
+        <v>-174100</v>
       </c>
       <c r="F94" s="3">
-        <v>-190200</v>
+        <v>-185400</v>
       </c>
       <c r="G94" s="3">
-        <v>-316000</v>
+        <v>-308000</v>
       </c>
       <c r="H94" s="3">
-        <v>-319000</v>
+        <v>-310900</v>
       </c>
       <c r="I94" s="3">
-        <v>-236000</v>
+        <v>-230000</v>
       </c>
       <c r="J94" s="3">
-        <v>-146400</v>
+        <v>-142700</v>
       </c>
       <c r="K94" s="3">
         <v>-278000</v>
@@ -7906,7 +7906,7 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-277600</v>
+        <v>-270600</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -8259,25 +8259,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>809400</v>
+        <v>788800</v>
       </c>
       <c r="E100" s="3">
-        <v>12700</v>
+        <v>12400</v>
       </c>
       <c r="F100" s="3">
-        <v>764200</v>
+        <v>744900</v>
       </c>
       <c r="G100" s="3">
-        <v>30000</v>
+        <v>29200</v>
       </c>
       <c r="H100" s="3">
-        <v>132300</v>
+        <v>129000</v>
       </c>
       <c r="I100" s="3">
-        <v>-387600</v>
+        <v>-377700</v>
       </c>
       <c r="J100" s="3">
-        <v>271600</v>
+        <v>264700</v>
       </c>
       <c r="K100" s="3">
         <v>-1291300</v>
@@ -8351,25 +8351,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>30400</v>
+        <v>29600</v>
       </c>
       <c r="E101" s="3">
-        <v>-64900</v>
+        <v>-63300</v>
       </c>
       <c r="F101" s="3">
-        <v>-15000</v>
+        <v>-14700</v>
       </c>
       <c r="G101" s="3">
-        <v>-39200</v>
+        <v>-38200</v>
       </c>
       <c r="H101" s="3">
-        <v>37300</v>
+        <v>36400</v>
       </c>
       <c r="I101" s="3">
-        <v>92400</v>
+        <v>90000</v>
       </c>
       <c r="J101" s="3">
-        <v>-181800</v>
+        <v>-177200</v>
       </c>
       <c r="K101" s="3">
         <v>39700</v>
@@ -8443,25 +8443,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>81600</v>
+        <v>79500</v>
       </c>
       <c r="E102" s="3">
-        <v>176200</v>
+        <v>171800</v>
       </c>
       <c r="F102" s="3">
-        <v>-17100</v>
+        <v>-16700</v>
       </c>
       <c r="G102" s="3">
-        <v>150000</v>
+        <v>146200</v>
       </c>
       <c r="H102" s="3">
-        <v>454300</v>
+        <v>442800</v>
       </c>
       <c r="I102" s="3">
-        <v>-120700</v>
+        <v>-117600</v>
       </c>
       <c r="J102" s="3">
-        <v>294900</v>
+        <v>287400</v>
       </c>
       <c r="K102" s="3">
         <v>-675200</v>

--- a/AAII_Financials/Quarterly/BAK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
   <si>
     <t>BAK</t>
   </si>
@@ -656,416 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3342100</v>
+        <v>3310900</v>
       </c>
       <c r="E8" s="3">
-        <v>3558700</v>
+        <v>3083900</v>
       </c>
       <c r="F8" s="3">
-        <v>3897400</v>
+        <v>3081000</v>
       </c>
       <c r="G8" s="3">
-        <v>3805900</v>
+        <v>3280600</v>
       </c>
       <c r="H8" s="3">
-        <v>5088000</v>
+        <v>3592800</v>
       </c>
       <c r="I8" s="3">
+        <v>3508600</v>
+      </c>
+      <c r="J8" s="3">
+        <v>4690500</v>
+      </c>
+      <c r="K8" s="3">
         <v>5092900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>5357500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>5694300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>5699500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>5116000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4393900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3505800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>3114900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2204800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>2487800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2334600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2507600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>2361600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>2428600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>2646900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>3024900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>4961600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>3042500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>3237700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>3118100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>3043300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>3125700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>2988400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>2972300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3228000</v>
+        <v>3087200</v>
       </c>
       <c r="E9" s="3">
-        <v>3466800</v>
+        <v>2897600</v>
       </c>
       <c r="F9" s="3">
-        <v>3700000</v>
+        <v>2975800</v>
       </c>
       <c r="G9" s="3">
-        <v>3821600</v>
+        <v>3195900</v>
       </c>
       <c r="H9" s="3">
-        <v>4641400</v>
+        <v>3410900</v>
       </c>
       <c r="I9" s="3">
+        <v>3523000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>4278700</v>
+      </c>
+      <c r="K9" s="3">
         <v>4275500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>4329400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>4341600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>4027000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>3216000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2992400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>2581500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>2420400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1902700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>2256600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2043700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>2185500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>2071700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>2107800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>2300800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>2358800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>3868600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2411600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>2405700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>2349100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2319300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>2210800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>2269000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>2174500</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>114100</v>
+        <v>223700</v>
       </c>
       <c r="E10" s="3">
-        <v>91900</v>
+        <v>186300</v>
       </c>
       <c r="F10" s="3">
-        <v>197400</v>
+        <v>105100</v>
       </c>
       <c r="G10" s="3">
-        <v>-15700</v>
+        <v>84700</v>
       </c>
       <c r="H10" s="3">
-        <v>446600</v>
+        <v>181900</v>
       </c>
       <c r="I10" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>411700</v>
+      </c>
+      <c r="K10" s="3">
         <v>817400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1028100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1352700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1672600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1900000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1401500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>924300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>694500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>302100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>231200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>291000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>322100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>289900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>320800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>346100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>666100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1093000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>630900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>831900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>769000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>724100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>914900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>719400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>797900</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,100 +1123,108 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>18500</v>
+        <v>19600</v>
       </c>
       <c r="E12" s="3">
-        <v>16300</v>
+        <v>21400</v>
       </c>
       <c r="F12" s="3">
-        <v>18800</v>
+        <v>17000</v>
       </c>
       <c r="G12" s="3">
-        <v>23900</v>
+        <v>15000</v>
       </c>
       <c r="H12" s="3">
-        <v>20900</v>
+        <v>17300</v>
       </c>
       <c r="I12" s="3">
+        <v>22000</v>
+      </c>
+      <c r="J12" s="3">
+        <v>19300</v>
+      </c>
+      <c r="K12" s="3">
         <v>15700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>14600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>19900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>14900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>12000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>12000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>14600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>12300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>10600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>10900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>14400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>11000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>9900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>10300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>11700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>10700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>17700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>9100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>14500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>10000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>9900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>8400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>10500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1282,100 +1315,112 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E14" s="3">
+        <v>189000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>19200</v>
+      </c>
+      <c r="G14" s="3">
+        <v>198200</v>
+      </c>
+      <c r="H14" s="3">
+        <v>27200</v>
+      </c>
+      <c r="I14" s="3">
+        <v>17400</v>
+      </c>
+      <c r="J14" s="3">
+        <v>27300</v>
+      </c>
+      <c r="K14" s="3">
+        <v>238100</v>
+      </c>
+      <c r="L14" s="3">
+        <v>23800</v>
+      </c>
+      <c r="M14" s="3">
+        <v>332300</v>
+      </c>
+      <c r="N14" s="3">
+        <v>48100</v>
+      </c>
+      <c r="O14" s="3">
+        <v>-105900</v>
+      </c>
+      <c r="P14" s="3">
+        <v>-121000</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>358600</v>
+      </c>
+      <c r="R14" s="3">
+        <v>627600</v>
+      </c>
+      <c r="S14" s="3">
+        <v>290800</v>
+      </c>
+      <c r="T14" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="U14" s="3">
+        <v>651700</v>
+      </c>
+      <c r="V14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="3">
-        <v>215100</v>
-      </c>
-      <c r="F14" s="3">
-        <v>29500</v>
-      </c>
-      <c r="G14" s="3">
-        <v>18800</v>
-      </c>
-      <c r="H14" s="3">
-        <v>29700</v>
-      </c>
-      <c r="I14" s="3">
-        <v>238100</v>
-      </c>
-      <c r="J14" s="3">
-        <v>23800</v>
-      </c>
-      <c r="K14" s="3">
-        <v>332300</v>
-      </c>
-      <c r="L14" s="3">
-        <v>48100</v>
-      </c>
-      <c r="M14" s="3">
-        <v>-105900</v>
-      </c>
-      <c r="N14" s="3">
-        <v>-121000</v>
-      </c>
-      <c r="O14" s="3">
-        <v>358600</v>
-      </c>
-      <c r="P14" s="3">
-        <v>627600</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>290800</v>
-      </c>
-      <c r="R14" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="S14" s="3">
-        <v>651700</v>
-      </c>
-      <c r="T14" s="3" t="s">
+      <c r="W14" s="3">
+        <v>77000</v>
+      </c>
+      <c r="X14" s="3">
+        <v>60800</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>15100</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>10600</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>-65200</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>26900</v>
+      </c>
+      <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U14" s="3">
-        <v>77000</v>
-      </c>
-      <c r="V14" s="3">
-        <v>60800</v>
-      </c>
-      <c r="W14" s="3">
-        <v>-15700</v>
-      </c>
-      <c r="X14" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>-30900</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>15100</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>10600</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>-65200</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>-700</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>26900</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1548,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>10</v>
+      <c r="D17" s="3">
+        <v>3318500</v>
       </c>
       <c r="E17" s="3">
-        <v>3887400</v>
+        <v>3273800</v>
       </c>
       <c r="F17" s="3">
-        <v>3798000</v>
+        <v>3195500</v>
       </c>
       <c r="G17" s="3">
-        <v>4175300</v>
+        <v>3583700</v>
       </c>
       <c r="H17" s="3">
-        <v>4949700</v>
+        <v>3501200</v>
       </c>
       <c r="I17" s="3">
+        <v>3849100</v>
+      </c>
+      <c r="J17" s="3">
+        <v>4562900</v>
+      </c>
+      <c r="K17" s="3">
         <v>4761300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4601900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4943100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4386700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3361100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3088800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3294100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>3228800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2401000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2413500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2994600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2402800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>2212400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2032800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2439400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>2508600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>4156600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2595500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2671600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>2622900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>2450700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>2404300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>3295900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>2402600</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>10</v>
+      <c r="D18" s="3">
+        <v>-7600</v>
       </c>
       <c r="E18" s="3">
-        <v>-328700</v>
+        <v>-189900</v>
       </c>
       <c r="F18" s="3">
-        <v>99400</v>
+        <v>-114600</v>
       </c>
       <c r="G18" s="3">
-        <v>-369400</v>
+        <v>-303000</v>
       </c>
       <c r="H18" s="3">
-        <v>138300</v>
+        <v>91600</v>
       </c>
       <c r="I18" s="3">
+        <v>-340500</v>
+      </c>
+      <c r="J18" s="3">
+        <v>127500</v>
+      </c>
+      <c r="K18" s="3">
         <v>331600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>755600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>751200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1312900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1754900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1305000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>211600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-113800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-196200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>74300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-660000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>104800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>149300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>395800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>207500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>516300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>805000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>447000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>566000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>495200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>592600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>721500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-307500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>569700</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1780,500 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>10</v>
+      <c r="D20" s="3">
+        <v>-167200</v>
       </c>
       <c r="E20" s="3">
-        <v>219600</v>
+        <v>49900</v>
       </c>
       <c r="F20" s="3">
-        <v>140300</v>
+        <v>-259600</v>
       </c>
       <c r="G20" s="3">
-        <v>101800</v>
+        <v>202500</v>
       </c>
       <c r="H20" s="3">
-        <v>-160900</v>
+        <v>129400</v>
       </c>
       <c r="I20" s="3">
+        <v>93900</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-148300</v>
+      </c>
+      <c r="K20" s="3">
         <v>-508000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>387400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-334000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-462000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>299500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-500400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>305900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-205200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-324000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-1075200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-51500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-381300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-61000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-70600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-102900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-70400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-297800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-365400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-99500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-26500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>46800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-229800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-283500</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>10</v>
+      <c r="D21" s="3">
+        <v>52300</v>
       </c>
       <c r="E21" s="3">
-        <v>152300</v>
+        <v>116100</v>
       </c>
       <c r="F21" s="3">
-        <v>486400</v>
+        <v>-136700</v>
       </c>
       <c r="G21" s="3">
-        <v>19300</v>
+        <v>140400</v>
       </c>
       <c r="H21" s="3">
-        <v>213300</v>
+        <v>448400</v>
       </c>
       <c r="I21" s="3">
+        <v>17800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>196600</v>
+      </c>
+      <c r="K21" s="3">
         <v>47200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1345400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>692900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1044000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2233000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>985100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>713300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-112800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-329100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-809100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-522300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-112000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>242200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>486500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>236900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>591800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>777500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>616300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>395300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>586700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>751200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>942400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-356700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>462600</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="3">
+        <v>207900</v>
+      </c>
+      <c r="E22" s="3">
+        <v>197500</v>
+      </c>
+      <c r="F22" s="3">
+        <v>185700</v>
+      </c>
+      <c r="G22" s="3">
+        <v>172800</v>
+      </c>
+      <c r="H22" s="3">
+        <v>194400</v>
+      </c>
+      <c r="I22" s="3">
+        <v>164800</v>
+      </c>
+      <c r="J22" s="3">
+        <v>165000</v>
+      </c>
+      <c r="K22" s="3">
+        <v>172000</v>
+      </c>
+      <c r="L22" s="3">
+        <v>137300</v>
+      </c>
+      <c r="M22" s="3">
+        <v>165300</v>
+      </c>
+      <c r="N22" s="3">
+        <v>163000</v>
+      </c>
+      <c r="O22" s="3">
+        <v>114100</v>
+      </c>
+      <c r="P22" s="3">
+        <v>170300</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>137900</v>
+      </c>
+      <c r="R22" s="3">
+        <v>151600</v>
+      </c>
+      <c r="S22" s="3">
+        <v>153700</v>
+      </c>
+      <c r="T22" s="3">
+        <v>157200</v>
+      </c>
+      <c r="U22" s="3">
+        <v>109600</v>
+      </c>
+      <c r="V22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="3">
-        <v>187400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>210900</v>
-      </c>
-      <c r="G22" s="3">
-        <v>178800</v>
-      </c>
-      <c r="H22" s="3">
-        <v>179000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>172000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>137300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>165300</v>
-      </c>
-      <c r="L22" s="3">
-        <v>163000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>114100</v>
-      </c>
-      <c r="N22" s="3">
-        <v>170300</v>
-      </c>
-      <c r="O22" s="3">
-        <v>137900</v>
-      </c>
-      <c r="P22" s="3">
-        <v>151600</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>153700</v>
-      </c>
-      <c r="R22" s="3">
-        <v>157200</v>
-      </c>
-      <c r="S22" s="3">
-        <v>109600</v>
-      </c>
-      <c r="T22" s="3" t="s">
+      <c r="W22" s="3">
+        <v>101700</v>
+      </c>
+      <c r="X22" s="3">
+        <v>102100</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>91800</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>101900</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>188500</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>110300</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>131700</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>141600</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>147200</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>142400</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>159500</v>
+      </c>
+      <c r="AH22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U22" s="3">
-        <v>101700</v>
-      </c>
-      <c r="V22" s="3">
-        <v>102100</v>
-      </c>
-      <c r="W22" s="3">
-        <v>91800</v>
-      </c>
-      <c r="X22" s="3">
-        <v>101900</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>188500</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>110300</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>131700</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>141600</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>147200</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>142400</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>159500</v>
-      </c>
-      <c r="AF22" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-607300</v>
+        <v>-382600</v>
       </c>
       <c r="E23" s="3">
-        <v>-296500</v>
+        <v>-337400</v>
       </c>
       <c r="F23" s="3">
-        <v>28900</v>
+        <v>-559900</v>
       </c>
       <c r="G23" s="3">
-        <v>-446300</v>
+        <v>-273400</v>
       </c>
       <c r="H23" s="3">
-        <v>-201500</v>
+        <v>26600</v>
       </c>
       <c r="I23" s="3">
+        <v>-411400</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-185800</v>
+      </c>
+      <c r="K23" s="3">
         <v>-348300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1005600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>251900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>687900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1940300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>634400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>379600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-470600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-673800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1158100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-821100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-276500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-13400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>223100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>12800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>344000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>318600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>333200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>68800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>254200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>418900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>625800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-696900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>286200</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-94600</v>
+        <v>-125800</v>
       </c>
       <c r="E24" s="3">
-        <v>-131500</v>
+        <v>-13900</v>
       </c>
       <c r="F24" s="3">
-        <v>-19700</v>
+        <v>-87200</v>
       </c>
       <c r="G24" s="3">
-        <v>-68900</v>
+        <v>-121200</v>
       </c>
       <c r="H24" s="3">
-        <v>83500</v>
+        <v>-18200</v>
       </c>
       <c r="I24" s="3">
+        <v>-63500</v>
+      </c>
+      <c r="J24" s="3">
+        <v>76900</v>
+      </c>
+      <c r="K24" s="3">
         <v>-55200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>214500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>157400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-20500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>476000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>167100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>215400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-210100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-181900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-358300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-288200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-91400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-23600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>51500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>44600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>77100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>14500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>64500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-11400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>58400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>126000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>153200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-46600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>84600</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-512700</v>
+        <v>-256800</v>
       </c>
       <c r="E26" s="3">
-        <v>-165000</v>
+        <v>-323500</v>
       </c>
       <c r="F26" s="3">
-        <v>48600</v>
+        <v>-472600</v>
       </c>
       <c r="G26" s="3">
-        <v>-377400</v>
+        <v>-152100</v>
       </c>
       <c r="H26" s="3">
-        <v>-285000</v>
+        <v>44800</v>
       </c>
       <c r="I26" s="3">
+        <v>-348000</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-262700</v>
+      </c>
+      <c r="K26" s="3">
         <v>-293200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>791100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>94500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>708500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1464200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>467400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>164200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-260500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-492000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-799900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-532900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-185000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>10200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>171600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-31900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>266800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>304100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>268800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>80200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>195800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>292900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>472700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-650200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>201700</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-484700</v>
+        <v>-248500</v>
       </c>
       <c r="E27" s="3">
-        <v>-154400</v>
+        <v>-290900</v>
       </c>
       <c r="F27" s="3">
-        <v>37000</v>
+        <v>-446800</v>
       </c>
       <c r="G27" s="3">
-        <v>-342800</v>
+        <v>-142400</v>
       </c>
       <c r="H27" s="3">
-        <v>-221100</v>
+        <v>34100</v>
       </c>
       <c r="I27" s="3">
+        <v>-316000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-203800</v>
+      </c>
+      <c r="K27" s="3">
         <v>-281800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>778400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>107000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>712300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1437400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>483000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>158300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-275200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-487900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-719100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-539700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-166500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>14900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>173700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-14000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>248700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>296200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>246000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>99000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>204900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>279400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>446200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-628800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>219400</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2627,16 +2748,22 @@
         <v>0</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>2200</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AG29" s="3">
         <v>900</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AH29" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2952,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>10</v>
+      <c r="D32" s="3">
+        <v>167200</v>
       </c>
       <c r="E32" s="3">
-        <v>-219600</v>
+        <v>-49900</v>
       </c>
       <c r="F32" s="3">
-        <v>-140300</v>
+        <v>259600</v>
       </c>
       <c r="G32" s="3">
-        <v>-101800</v>
+        <v>-202500</v>
       </c>
       <c r="H32" s="3">
-        <v>160900</v>
+        <v>-129400</v>
       </c>
       <c r="I32" s="3">
+        <v>-93900</v>
+      </c>
+      <c r="J32" s="3">
+        <v>148300</v>
+      </c>
+      <c r="K32" s="3">
         <v>508000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-387400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>334000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>462000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-299500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>500400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-305900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>205200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>324000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>1075200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>51500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>381300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>61000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>70600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>102900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>70400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>297800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>3400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>365400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>99500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>26500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-46800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>229800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>283500</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-484700</v>
+        <v>-248500</v>
       </c>
       <c r="E33" s="3">
-        <v>-154400</v>
+        <v>-290900</v>
       </c>
       <c r="F33" s="3">
-        <v>37000</v>
+        <v>-446800</v>
       </c>
       <c r="G33" s="3">
-        <v>-342800</v>
+        <v>-142400</v>
       </c>
       <c r="H33" s="3">
-        <v>-221100</v>
+        <v>34100</v>
       </c>
       <c r="I33" s="3">
+        <v>-316000</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-203800</v>
+      </c>
+      <c r="K33" s="3">
         <v>-281800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>778400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>107000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>712300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1437400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>483000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>158300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-275200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-487900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-719100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-539700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-166500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>14900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>173700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-14000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>248700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>296200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>246000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>99000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>204900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>279400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>448400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-628000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>220700</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-484700</v>
+        <v>-248500</v>
       </c>
       <c r="E35" s="3">
-        <v>-154400</v>
+        <v>-290900</v>
       </c>
       <c r="F35" s="3">
-        <v>37000</v>
+        <v>-446800</v>
       </c>
       <c r="G35" s="3">
-        <v>-342800</v>
+        <v>-142400</v>
       </c>
       <c r="H35" s="3">
-        <v>-221100</v>
+        <v>34100</v>
       </c>
       <c r="I35" s="3">
+        <v>-316000</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-203800</v>
+      </c>
+      <c r="K35" s="3">
         <v>-281800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>778400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>107000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>712300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1437400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>483000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>158300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-275200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-487900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-719100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-539700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-166500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>14900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>173700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-14000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>248700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>296200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>246000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>99000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>204900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>279400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>448400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-628000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>220700</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,836 +3523,892 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2733100</v>
+        <v>2626400</v>
       </c>
       <c r="E41" s="3">
-        <v>2653600</v>
+        <v>2621200</v>
       </c>
       <c r="F41" s="3">
-        <v>2481800</v>
+        <v>2519500</v>
       </c>
       <c r="G41" s="3">
-        <v>2498500</v>
+        <v>2446300</v>
       </c>
       <c r="H41" s="3">
-        <v>2352400</v>
+        <v>2287900</v>
       </c>
       <c r="I41" s="3">
+        <v>2303300</v>
+      </c>
+      <c r="J41" s="3">
+        <v>2168600</v>
+      </c>
+      <c r="K41" s="3">
         <v>1909600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2027200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1752100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2422000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1890800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2419100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2593600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2400500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2953000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1981600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1256700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1072000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1024900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1142200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>989700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>905000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>952900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>797100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>967900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>1397900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1464300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>1641600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>1662600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>2034300</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1010600</v>
+        <v>731600</v>
       </c>
       <c r="E42" s="3">
-        <v>469000</v>
+        <v>915700</v>
       </c>
       <c r="F42" s="3">
-        <v>767300</v>
+        <v>931600</v>
       </c>
       <c r="G42" s="3">
-        <v>460100</v>
+        <v>432400</v>
       </c>
       <c r="H42" s="3">
-        <v>499400</v>
+        <v>707300</v>
       </c>
       <c r="I42" s="3">
+        <v>424100</v>
+      </c>
+      <c r="J42" s="3">
+        <v>460400</v>
+      </c>
+      <c r="K42" s="3">
         <v>766700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>416000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>705000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>591300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>736800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>751000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>678600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>624200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>542500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>451600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>311700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>241600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>120300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>321900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>420600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>385000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>380400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>569800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>590400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>585700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>686500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>250900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>295300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>107400</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1194200</v>
+        <v>957400</v>
       </c>
       <c r="E43" s="3">
-        <v>1103300</v>
+        <v>886700</v>
       </c>
       <c r="F43" s="3">
-        <v>1296800</v>
+        <v>1100900</v>
       </c>
       <c r="G43" s="3">
-        <v>1103900</v>
+        <v>1017100</v>
       </c>
       <c r="H43" s="3">
-        <v>1830300</v>
+        <v>1195500</v>
       </c>
       <c r="I43" s="3">
+        <v>1017600</v>
+      </c>
+      <c r="J43" s="3">
+        <v>1687300</v>
+      </c>
+      <c r="K43" s="3">
         <v>1889000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1979000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2082100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2738400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2403300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2135000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1485100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1319700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1157500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1084200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1321200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1026100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>893800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>861400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>842900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1091300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>836300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1029700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>1263800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1077900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1019500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>752400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>658900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>796900</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2500400</v>
+        <v>2449200</v>
       </c>
       <c r="E44" s="3">
-        <v>2602400</v>
+        <v>2315400</v>
       </c>
       <c r="F44" s="3">
-        <v>2762100</v>
+        <v>2305100</v>
       </c>
       <c r="G44" s="3">
-        <v>2811900</v>
+        <v>2399000</v>
       </c>
       <c r="H44" s="3">
-        <v>3009000</v>
+        <v>2546300</v>
       </c>
       <c r="I44" s="3">
+        <v>2592200</v>
+      </c>
+      <c r="J44" s="3">
+        <v>2773900</v>
+      </c>
+      <c r="K44" s="3">
         <v>3411700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>3396800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>3297100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>2893300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>2460700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>2311800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1568500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1571000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1452200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>1543800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1408400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>1476000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>1464000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>1515400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>1514000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>1655100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>1501300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>1559800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>1755400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>1473200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>1514600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>1375900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>1299400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>1209100</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>32400</v>
+        <v>155200</v>
       </c>
       <c r="E45" s="3">
-        <v>54000</v>
+        <v>178700</v>
       </c>
       <c r="F45" s="3">
-        <v>34700</v>
+        <v>29900</v>
       </c>
       <c r="G45" s="3">
-        <v>31600</v>
+        <v>49800</v>
       </c>
       <c r="H45" s="3">
-        <v>11300</v>
+        <v>32000</v>
       </c>
       <c r="I45" s="3">
+        <v>29200</v>
+      </c>
+      <c r="J45" s="3">
+        <v>10400</v>
+      </c>
+      <c r="K45" s="3">
         <v>18500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>149300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>94700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>39100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>67600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>69200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>70800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>84700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>79500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>18600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>22100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>29700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>39900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>59800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>47700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>24700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>29100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>31200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>35400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>51200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>52400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>111400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>116600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7470800</v>
+        <v>6919800</v>
       </c>
       <c r="E46" s="3">
-        <v>6882200</v>
+        <v>6917600</v>
       </c>
       <c r="F46" s="3">
-        <v>7342700</v>
+        <v>6887100</v>
       </c>
       <c r="G46" s="3">
-        <v>6906000</v>
+        <v>6344500</v>
       </c>
       <c r="H46" s="3">
-        <v>7702400</v>
+        <v>6769000</v>
       </c>
       <c r="I46" s="3">
+        <v>6366400</v>
+      </c>
+      <c r="J46" s="3">
+        <v>7100500</v>
+      </c>
+      <c r="K46" s="3">
         <v>7995400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>7968300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>7931000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>8684100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>7559200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>7686000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>6396700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>6000200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>6184600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>5079800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>4320100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>3845500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>3542900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>3900600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3814900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>4061100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>3700000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>3987600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>4612900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>4585900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>4737400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>4132100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>4032900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>4186700</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1478500</v>
+        <v>389100</v>
       </c>
       <c r="E47" s="3">
-        <v>469000</v>
+        <v>376400</v>
       </c>
       <c r="F47" s="3">
-        <v>466600</v>
+        <v>431300</v>
       </c>
       <c r="G47" s="3">
-        <v>442400</v>
+        <v>432400</v>
       </c>
       <c r="H47" s="3">
-        <v>472400</v>
+        <v>430100</v>
       </c>
       <c r="I47" s="3">
+        <v>407800</v>
+      </c>
+      <c r="J47" s="3">
+        <v>435500</v>
+      </c>
+      <c r="K47" s="3">
         <v>438300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>376400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>391000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>360300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>444500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>291700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>272100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>454400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>516900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>628100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>511200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>441100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>506500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>562700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>338000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>238400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>250800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>309100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>329600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>378500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>380000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>362800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>345300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>426900</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>8441400</v>
+        <v>7844400</v>
       </c>
       <c r="E48" s="3">
-        <v>8335600</v>
+        <v>7801500</v>
       </c>
       <c r="F48" s="3">
-        <v>8442800</v>
+        <v>7781800</v>
       </c>
       <c r="G48" s="3">
-        <v>8360800</v>
+        <v>7684300</v>
       </c>
       <c r="H48" s="3">
-        <v>8239900</v>
+        <v>7783100</v>
       </c>
       <c r="I48" s="3">
+        <v>7707500</v>
+      </c>
+      <c r="J48" s="3">
+        <v>7596100</v>
+      </c>
+      <c r="K48" s="3">
         <v>7898100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>7344600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>8074600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>7859700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>7278100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>7805500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>7265000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>7612900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>7485700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>7310600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>6449900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>6356800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>5860000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>6264500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>5666000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>6059100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>5851700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>7088700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>7630300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>7640900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>7806300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>7344800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>7277900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>7403700</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>622700</v>
+        <v>576300</v>
       </c>
       <c r="E49" s="3">
-        <v>617000</v>
+        <v>574200</v>
       </c>
       <c r="F49" s="3">
-        <v>618100</v>
+        <v>574100</v>
       </c>
       <c r="G49" s="3">
-        <v>605700</v>
+        <v>568800</v>
       </c>
       <c r="H49" s="3">
-        <v>590000</v>
+        <v>569800</v>
       </c>
       <c r="I49" s="3">
+        <v>558400</v>
+      </c>
+      <c r="J49" s="3">
+        <v>543900</v>
+      </c>
+      <c r="K49" s="3">
         <v>571400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>565400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>580800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>569800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>543300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>550000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>529200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>547400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>548300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>546700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>510200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>515400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>483000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>510800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>489000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>508500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>506900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>633500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>699300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>704400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>714300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>689900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>696900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>699100</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4597,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>80100</v>
+        <v>1553300</v>
       </c>
       <c r="E52" s="3">
-        <v>1334900</v>
+        <v>1280400</v>
       </c>
       <c r="F52" s="3">
-        <v>1257700</v>
+        <v>1326400</v>
       </c>
       <c r="G52" s="3">
-        <v>1331900</v>
+        <v>1230600</v>
       </c>
       <c r="H52" s="3">
-        <v>1475900</v>
+        <v>1159400</v>
       </c>
       <c r="I52" s="3">
+        <v>1227800</v>
+      </c>
+      <c r="J52" s="3">
+        <v>1360500</v>
+      </c>
+      <c r="K52" s="3">
         <v>1489300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1168100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1705900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1545100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1201600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1881700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1642500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>2165100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1926900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1643300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>792100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1120900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>905000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>258100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>252400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>381100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>451100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>313100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>403600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>326100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>353300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>386600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>503100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>457300</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>18441700</v>
+        <v>17282800</v>
       </c>
       <c r="E54" s="3">
-        <v>17638800</v>
+        <v>16950100</v>
       </c>
       <c r="F54" s="3">
-        <v>18127900</v>
+        <v>17000800</v>
       </c>
       <c r="G54" s="3">
-        <v>17646800</v>
+        <v>16260600</v>
       </c>
       <c r="H54" s="3">
-        <v>18480500</v>
+        <v>16711400</v>
       </c>
       <c r="I54" s="3">
+        <v>16267900</v>
+      </c>
+      <c r="J54" s="3">
+        <v>17036500</v>
+      </c>
+      <c r="K54" s="3">
         <v>18392400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>17422800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>18683200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>19019100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>17026700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>18214800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>16105400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>16780100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>16662500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>15208500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>12583400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>12279700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>11297500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>11496800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>10560200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>11248200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>10760600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>12332000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>13675700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>13635900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>13991200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>12916200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>12856000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>13173700</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4967,598 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2661200</v>
+        <v>2752700</v>
       </c>
       <c r="E57" s="3">
-        <v>2397700</v>
+        <v>2442700</v>
       </c>
       <c r="F57" s="3">
-        <v>2453800</v>
+        <v>2453200</v>
       </c>
       <c r="G57" s="3">
-        <v>2454500</v>
+        <v>2210300</v>
       </c>
       <c r="H57" s="3">
-        <v>2577200</v>
+        <v>2262100</v>
       </c>
       <c r="I57" s="3">
+        <v>2262700</v>
+      </c>
+      <c r="J57" s="3">
+        <v>2375900</v>
+      </c>
+      <c r="K57" s="3">
         <v>2547700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2415800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2432800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2102200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2067800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2653800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1860900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1727400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1688200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1944600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1683900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1707000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1614000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1543200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1488100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1736200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1528000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1323600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>1350000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>1233400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1348000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>1257900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>1623700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>1777600</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>673900</v>
+        <v>584200</v>
       </c>
       <c r="E58" s="3">
-        <v>702600</v>
+        <v>692100</v>
       </c>
       <c r="F58" s="3">
-        <v>669000</v>
+        <v>621300</v>
       </c>
       <c r="G58" s="3">
-        <v>659500</v>
+        <v>647700</v>
       </c>
       <c r="H58" s="3">
-        <v>507800</v>
+        <v>616800</v>
       </c>
       <c r="I58" s="3">
+        <v>608000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>468100</v>
+      </c>
+      <c r="K58" s="3">
         <v>533800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>614800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>436900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1812300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1976400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2022700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1857500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>672200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1099500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>786300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>414200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>2599500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>2298100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>2118700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>2010500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>2235800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>2243600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>2379100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>2795400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>3374100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>3695000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>3205900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>3233000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>731800</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1511100</v>
+        <v>1458100</v>
       </c>
       <c r="E59" s="3">
-        <v>1531900</v>
+        <v>1390700</v>
       </c>
       <c r="F59" s="3">
-        <v>1698700</v>
+        <v>1393000</v>
       </c>
       <c r="G59" s="3">
-        <v>1733200</v>
+        <v>1412200</v>
       </c>
       <c r="H59" s="3">
-        <v>1943800</v>
+        <v>1566000</v>
       </c>
       <c r="I59" s="3">
+        <v>1597800</v>
+      </c>
+      <c r="J59" s="3">
+        <v>1791900</v>
+      </c>
+      <c r="K59" s="3">
         <v>2068000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1853600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2215300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2603500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1966700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1796200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1592600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1664100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1451600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1196900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>897100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>679000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>571900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>546700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>625300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>522000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>498700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>526100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>761100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>719900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>760100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>881200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>858600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>814100</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4846200</v>
+        <v>4795100</v>
       </c>
       <c r="E60" s="3">
-        <v>4632100</v>
+        <v>4525500</v>
       </c>
       <c r="F60" s="3">
-        <v>4821500</v>
+        <v>4467500</v>
       </c>
       <c r="G60" s="3">
-        <v>4847200</v>
+        <v>4270200</v>
       </c>
       <c r="H60" s="3">
-        <v>5028800</v>
+        <v>4444800</v>
       </c>
       <c r="I60" s="3">
+        <v>4468500</v>
+      </c>
+      <c r="J60" s="3">
+        <v>4635900</v>
+      </c>
+      <c r="K60" s="3">
         <v>5149500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4884200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>5085100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>6518000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>6010900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>6472700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>5311000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>4063700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>4239400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>3927700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2995100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>4985500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>4483900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>4208600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>4123900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>4494000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>4270300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>4228800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>4906500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>5327400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>5803000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>5344900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>5715300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>3323500</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10839300</v>
+        <v>10201500</v>
       </c>
       <c r="E61" s="3">
-        <v>9666200</v>
+        <v>9916600</v>
       </c>
       <c r="F61" s="3">
-        <v>10100600</v>
+        <v>9992400</v>
       </c>
       <c r="G61" s="3">
-        <v>9627600</v>
+        <v>8910900</v>
       </c>
       <c r="H61" s="3">
-        <v>9900200</v>
+        <v>9311400</v>
       </c>
       <c r="I61" s="3">
+        <v>8875300</v>
+      </c>
+      <c r="J61" s="3">
+        <v>9126600</v>
+      </c>
+      <c r="K61" s="3">
         <v>9348200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>8260900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>9768500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>7992100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>7319500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>9345600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>8850600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>11502700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>11478900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>10039400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>7334000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>4956900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>4362300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>4937800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>4310300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>4438500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>4496800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>4981500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>5685600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>4740400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>4970200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>4871100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>5144300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>7597500</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4539900</v>
+        <v>1848700</v>
       </c>
       <c r="E62" s="3">
-        <v>1989100</v>
+        <v>1902100</v>
       </c>
       <c r="F62" s="3">
-        <v>1772200</v>
+        <v>1732000</v>
       </c>
       <c r="G62" s="3">
-        <v>1947800</v>
+        <v>1833700</v>
       </c>
       <c r="H62" s="3">
-        <v>2182800</v>
+        <v>1633700</v>
       </c>
       <c r="I62" s="3">
+        <v>1795600</v>
+      </c>
+      <c r="J62" s="3">
+        <v>2012300</v>
+      </c>
+      <c r="K62" s="3">
         <v>2293800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2215500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>2577400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>2266500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2308600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2685000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>2667200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2462700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1996200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1806400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1525700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1173400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1112200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1004100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1071500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>1129300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>1096400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>1408600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1624600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1772800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1746400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>1575400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>1569400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>1162700</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>17435100</v>
+        <v>16713200</v>
       </c>
       <c r="E66" s="3">
-        <v>16189300</v>
+        <v>16212500</v>
       </c>
       <c r="F66" s="3">
-        <v>16559200</v>
+        <v>16072800</v>
       </c>
       <c r="G66" s="3">
-        <v>16179300</v>
+        <v>14924300</v>
       </c>
       <c r="H66" s="3">
-        <v>16739000</v>
+        <v>15265400</v>
       </c>
       <c r="I66" s="3">
+        <v>14915100</v>
+      </c>
+      <c r="J66" s="3">
+        <v>15431100</v>
+      </c>
+      <c r="K66" s="3">
         <v>16494600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>15098200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>17095600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>16448400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>15349800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>18131500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>16517500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>17649700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>17328600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>15405600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>11681100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>10917200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>9805200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>9987100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>9349300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>9920900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>9696800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>10466600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>12004700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>11654000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>12338600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>11595600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>12176600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>11845300</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-233800</v>
+        <v>-754000</v>
       </c>
       <c r="E72" s="3">
-        <v>250300</v>
+        <v>-505900</v>
       </c>
       <c r="F72" s="3">
-        <v>405400</v>
+        <v>-215500</v>
       </c>
       <c r="G72" s="3">
-        <v>367100</v>
+        <v>230800</v>
       </c>
       <c r="H72" s="3">
-        <v>708400</v>
+        <v>373800</v>
       </c>
       <c r="I72" s="3">
+        <v>338400</v>
+      </c>
+      <c r="J72" s="3">
+        <v>653100</v>
+      </c>
+      <c r="K72" s="3">
         <v>928100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1478700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>703900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1802600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1046900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-392800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-847400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-1047900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-783000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-296500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>394800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>947600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1050500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>1111600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>875200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>1044400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>794400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>1223400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>1071200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>1226800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1020100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>714900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>264700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>914200</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1006600</v>
+        <v>569600</v>
       </c>
       <c r="E76" s="3">
-        <v>1449600</v>
+        <v>737600</v>
       </c>
       <c r="F76" s="3">
-        <v>1568600</v>
+        <v>928000</v>
       </c>
       <c r="G76" s="3">
-        <v>1467400</v>
+        <v>1336300</v>
       </c>
       <c r="H76" s="3">
-        <v>1741500</v>
+        <v>1446100</v>
       </c>
       <c r="I76" s="3">
+        <v>1352800</v>
+      </c>
+      <c r="J76" s="3">
+        <v>1605400</v>
+      </c>
+      <c r="K76" s="3">
         <v>1897800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2324600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1587600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2570700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1676800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>83300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-412000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-869600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-666100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-197100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>902300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1362500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1492300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1509600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1210900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>1327200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>1063800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>1865400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>1671000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>1981900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>1652600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>1320600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>679400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>1328400</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-484700</v>
+        <v>-248500</v>
       </c>
       <c r="E81" s="3">
-        <v>-154400</v>
+        <v>-290900</v>
       </c>
       <c r="F81" s="3">
-        <v>37000</v>
+        <v>-446800</v>
       </c>
       <c r="G81" s="3">
-        <v>-342800</v>
+        <v>-142400</v>
       </c>
       <c r="H81" s="3">
-        <v>-221100</v>
+        <v>34100</v>
       </c>
       <c r="I81" s="3">
+        <v>-316000</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-203800</v>
+      </c>
+      <c r="K81" s="3">
         <v>-281800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>778400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>107000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>712300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1437400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>483000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>158300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-275200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-487900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-719100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-539700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-166500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>14900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>173700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-14000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>248700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>296200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>246000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>99000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>204900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>279400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>448400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-628000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>220700</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7200,108 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>257600</v>
+        <v>227100</v>
       </c>
       <c r="E83" s="3">
-        <v>261400</v>
+        <v>256100</v>
       </c>
       <c r="F83" s="3">
-        <v>246600</v>
+        <v>237500</v>
       </c>
       <c r="G83" s="3">
-        <v>286900</v>
+        <v>240900</v>
       </c>
       <c r="H83" s="3">
-        <v>235800</v>
+        <v>227300</v>
       </c>
       <c r="I83" s="3">
+        <v>264400</v>
+      </c>
+      <c r="J83" s="3">
+        <v>217300</v>
+      </c>
+      <c r="K83" s="3">
         <v>223600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>202400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>275600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>193100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>178600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>180400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>195800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>206200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>191000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>191800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>189200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>164500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>153900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>161300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>132300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>145800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>270300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>172800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>194800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>191000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>185100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>174200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>177700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>176400</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-493700</v>
+        <v>178300</v>
       </c>
       <c r="E89" s="3">
-        <v>396700</v>
+        <v>187300</v>
       </c>
       <c r="F89" s="3">
-        <v>-561500</v>
+        <v>-455200</v>
       </c>
       <c r="G89" s="3">
-        <v>463100</v>
+        <v>365700</v>
       </c>
       <c r="H89" s="3">
-        <v>588400</v>
+        <v>-517700</v>
       </c>
       <c r="I89" s="3">
+        <v>426900</v>
+      </c>
+      <c r="J89" s="3">
+        <v>542400</v>
+      </c>
+      <c r="K89" s="3">
         <v>400000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>342600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>854400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1155500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>486500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>446100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>718300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>189200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-129900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>422000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>169400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>150400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-88200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>195400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>179800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>391200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1133900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>420500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>341000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>377300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-232900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>141000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>179800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>704800</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7922,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1233000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1224500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-908300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1164300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1531300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1509900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-1108600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-698500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1378400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-819300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-142000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-94900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-155100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-88700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-112300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-178400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-164900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-118100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-124700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-85300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-160800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-122100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-211900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-94500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-187200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-198300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-120300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-67700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-418100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-262200</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +8212,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-245200</v>
+        <v>-160900</v>
       </c>
       <c r="E94" s="3">
-        <v>-174100</v>
+        <v>-278600</v>
       </c>
       <c r="F94" s="3">
-        <v>-185400</v>
+        <v>-226100</v>
       </c>
       <c r="G94" s="3">
-        <v>-308000</v>
+        <v>-160500</v>
       </c>
       <c r="H94" s="3">
-        <v>-310900</v>
+        <v>-170900</v>
       </c>
       <c r="I94" s="3">
+        <v>-283900</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-286600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-230000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-142700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-278000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-165000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-137300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-92000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-151100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-88700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-109600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-177800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-162900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-169800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-75000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-85300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-150800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-107300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-196700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-94200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-341100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-195500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-9900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-68200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-206800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-130100</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,44 +8350,46 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F96" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G96" s="3">
         <v>-500</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-270600</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-1209300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-400</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -7930,55 +8397,61 @@
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-500</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-123100</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-400</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-277500</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-256100</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-247800</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8738,304 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>788800</v>
+        <v>-48800</v>
       </c>
       <c r="E100" s="3">
-        <v>12400</v>
+        <v>214100</v>
       </c>
       <c r="F100" s="3">
-        <v>744900</v>
+        <v>727200</v>
       </c>
       <c r="G100" s="3">
-        <v>29200</v>
+        <v>11400</v>
       </c>
       <c r="H100" s="3">
-        <v>129000</v>
+        <v>686700</v>
       </c>
       <c r="I100" s="3">
+        <v>26900</v>
+      </c>
+      <c r="J100" s="3">
+        <v>118900</v>
+      </c>
+      <c r="K100" s="3">
         <v>-377700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>264700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1291300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-606100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-757400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-706100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-217000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-646300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>1126300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>184400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>212200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-24900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>123000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-13900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>73500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-297900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-630100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-405100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-416900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-275700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>35200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-105200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-237800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-197800</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>29600</v>
+        <v>36600</v>
       </c>
       <c r="E101" s="3">
-        <v>-63300</v>
+        <v>-21100</v>
       </c>
       <c r="F101" s="3">
-        <v>-14700</v>
+        <v>27300</v>
       </c>
       <c r="G101" s="3">
-        <v>-38200</v>
+        <v>-58300</v>
       </c>
       <c r="H101" s="3">
-        <v>36400</v>
+        <v>-13500</v>
       </c>
       <c r="I101" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="J101" s="3">
+        <v>33600</v>
+      </c>
+      <c r="K101" s="3">
         <v>90000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-177200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>39700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>71000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-120100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>86800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-62400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>27600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>84600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>212200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-17600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>30500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-15700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>7900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>14500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-33800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-52700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>27500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-24500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>11300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>14900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>79500</v>
+        <v>5200</v>
       </c>
       <c r="E102" s="3">
-        <v>171800</v>
+        <v>101700</v>
       </c>
       <c r="F102" s="3">
-        <v>-16700</v>
+        <v>73300</v>
       </c>
       <c r="G102" s="3">
-        <v>146200</v>
+        <v>158300</v>
       </c>
       <c r="H102" s="3">
-        <v>442800</v>
+        <v>-15400</v>
       </c>
       <c r="I102" s="3">
+        <v>134700</v>
+      </c>
+      <c r="J102" s="3">
+        <v>408200</v>
+      </c>
+      <c r="K102" s="3">
         <v>-117600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>287400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-675200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>455300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-528300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-265200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>287800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-518300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>971300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>640800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>201100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-13700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-55900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>104100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>117100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-47900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>254400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-84500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-430000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-66400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-232200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-21000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-254500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>362100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BAK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAK_QTR_FIN.xlsx
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3310900</v>
+        <v>3428300</v>
       </c>
       <c r="E8" s="3">
-        <v>3083900</v>
+        <v>3220800</v>
       </c>
       <c r="F8" s="3">
-        <v>3081000</v>
+        <v>2999900</v>
       </c>
       <c r="G8" s="3">
-        <v>3280600</v>
+        <v>2997100</v>
       </c>
       <c r="H8" s="3">
-        <v>3592800</v>
+        <v>3191300</v>
       </c>
       <c r="I8" s="3">
-        <v>3508600</v>
+        <v>3495000</v>
       </c>
       <c r="J8" s="3">
+        <v>3413000</v>
+      </c>
+      <c r="K8" s="3">
         <v>4690500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5092900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5357500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5694300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5699500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5116000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4393900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3505800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3114900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2204800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2487800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2334600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2507600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2361600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2428600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2646900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3024900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4961600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3042500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3237700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3118100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3043300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3125700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2988400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2972300</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3087200</v>
+        <v>3178500</v>
       </c>
       <c r="E9" s="3">
-        <v>2897600</v>
+        <v>3003100</v>
       </c>
       <c r="F9" s="3">
-        <v>2975800</v>
+        <v>2818700</v>
       </c>
       <c r="G9" s="3">
-        <v>3195900</v>
+        <v>2894800</v>
       </c>
       <c r="H9" s="3">
-        <v>3410900</v>
+        <v>3108900</v>
       </c>
       <c r="I9" s="3">
-        <v>3523000</v>
+        <v>3318000</v>
       </c>
       <c r="J9" s="3">
+        <v>3427100</v>
+      </c>
+      <c r="K9" s="3">
         <v>4278700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4275500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4329400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4341600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4027000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3216000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2992400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2581500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2420400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1902700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2256600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2043700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2185500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2071700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2107800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2300800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2358800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3868600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2411600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2405700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2349100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2319300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2210800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2269000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2174500</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>223700</v>
+        <v>249800</v>
       </c>
       <c r="E10" s="3">
-        <v>186300</v>
+        <v>217700</v>
       </c>
       <c r="F10" s="3">
-        <v>105100</v>
+        <v>181300</v>
       </c>
       <c r="G10" s="3">
-        <v>84700</v>
+        <v>102300</v>
       </c>
       <c r="H10" s="3">
-        <v>181900</v>
+        <v>82400</v>
       </c>
       <c r="I10" s="3">
-        <v>-14500</v>
+        <v>177000</v>
       </c>
       <c r="J10" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="K10" s="3">
         <v>411700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>817400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1028100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1352700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1672600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1900000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1401500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>924300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>694500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>302100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>231200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>291000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>322100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>289900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>320800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>346100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>666100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1093000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>630900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>831900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>769000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>724100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>914900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>719400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>797900</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,106 +1138,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>19600</v>
+        <v>19100</v>
       </c>
       <c r="E12" s="3">
+        <v>19100</v>
+      </c>
+      <c r="F12" s="3">
+        <v>20800</v>
+      </c>
+      <c r="G12" s="3">
+        <v>16500</v>
+      </c>
+      <c r="H12" s="3">
+        <v>14600</v>
+      </c>
+      <c r="I12" s="3">
+        <v>16800</v>
+      </c>
+      <c r="J12" s="3">
         <v>21400</v>
       </c>
-      <c r="F12" s="3">
-        <v>17000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>15000</v>
-      </c>
-      <c r="H12" s="3">
-        <v>17300</v>
-      </c>
-      <c r="I12" s="3">
-        <v>22000</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>19300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>15700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>14600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>19900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>14900</v>
-      </c>
-      <c r="O12" s="3">
-        <v>12000</v>
       </c>
       <c r="P12" s="3">
         <v>12000</v>
       </c>
       <c r="Q12" s="3">
+        <v>12000</v>
+      </c>
+      <c r="R12" s="3">
         <v>14600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>12300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>14400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>11000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>9900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>10300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>11700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>10700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>17700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>9100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>14500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>10000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>9900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>8400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>10500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1321,106 +1338,112 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>3500</v>
+        <v>68100</v>
       </c>
       <c r="E14" s="3">
-        <v>189000</v>
+        <v>3400</v>
       </c>
       <c r="F14" s="3">
-        <v>19200</v>
+        <v>183900</v>
       </c>
       <c r="G14" s="3">
-        <v>198200</v>
+        <v>18700</v>
       </c>
       <c r="H14" s="3">
-        <v>27200</v>
+        <v>192900</v>
       </c>
       <c r="I14" s="3">
-        <v>17400</v>
+        <v>26400</v>
       </c>
       <c r="J14" s="3">
+        <v>16900</v>
+      </c>
+      <c r="K14" s="3">
         <v>27300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>238100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>23800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>332300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>48100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-105900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-121000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>358600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>627600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>290800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-3000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>651700</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>77000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>60800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-30900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>15100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>10600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-65200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>26900</v>
       </c>
-      <c r="AH14" s="3" t="s">
+      <c r="AI14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3318500</v>
+        <v>3456600</v>
       </c>
       <c r="E17" s="3">
-        <v>3273800</v>
+        <v>3228100</v>
       </c>
       <c r="F17" s="3">
-        <v>3195500</v>
+        <v>3184600</v>
       </c>
       <c r="G17" s="3">
-        <v>3583700</v>
+        <v>3108500</v>
       </c>
       <c r="H17" s="3">
-        <v>3501200</v>
+        <v>3486100</v>
       </c>
       <c r="I17" s="3">
-        <v>3849100</v>
+        <v>3405900</v>
       </c>
       <c r="J17" s="3">
+        <v>3744300</v>
+      </c>
+      <c r="K17" s="3">
         <v>4562900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4761300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4601900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4943100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4386700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3361100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3088800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3294100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3228800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2401000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2413500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2994600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2402800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2212400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2032800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2439400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2508600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4156600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2595500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2671600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2622900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2450700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2404300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3295900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2402600</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-7600</v>
+        <v>-28200</v>
       </c>
       <c r="E18" s="3">
-        <v>-189900</v>
+        <v>-7400</v>
       </c>
       <c r="F18" s="3">
-        <v>-114600</v>
+        <v>-184700</v>
       </c>
       <c r="G18" s="3">
-        <v>-303000</v>
+        <v>-111500</v>
       </c>
       <c r="H18" s="3">
-        <v>91600</v>
+        <v>-294800</v>
       </c>
       <c r="I18" s="3">
-        <v>-340500</v>
+        <v>89100</v>
       </c>
       <c r="J18" s="3">
+        <v>-331200</v>
+      </c>
+      <c r="K18" s="3">
         <v>127500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>331600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>755600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>751200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1312900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1754900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1305000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>211600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-113800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-196200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>74300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-660000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>104800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>149300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>395800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>207500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>516300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>805000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>447000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>566000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>495200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>592600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>721500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-307500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>569700</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,498 +1815,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-167200</v>
+        <v>-831600</v>
       </c>
       <c r="E20" s="3">
-        <v>49900</v>
+        <v>-162700</v>
       </c>
       <c r="F20" s="3">
-        <v>-259600</v>
+        <v>48600</v>
       </c>
       <c r="G20" s="3">
-        <v>202500</v>
+        <v>-252600</v>
       </c>
       <c r="H20" s="3">
-        <v>129400</v>
+        <v>197000</v>
       </c>
       <c r="I20" s="3">
-        <v>93900</v>
+        <v>125900</v>
       </c>
       <c r="J20" s="3">
+        <v>91300</v>
+      </c>
+      <c r="K20" s="3">
         <v>-148300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-508000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>387400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-334000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-462000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>299500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-500400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>305900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-205200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-324000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1075200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-51500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-381300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-61000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-70600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-102900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-70400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-297800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-365400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-99500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-26500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>46800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-229800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-283500</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>52300</v>
+        <v>-628300</v>
       </c>
       <c r="E21" s="3">
-        <v>116100</v>
+        <v>50900</v>
       </c>
       <c r="F21" s="3">
-        <v>-136700</v>
+        <v>113000</v>
       </c>
       <c r="G21" s="3">
-        <v>140400</v>
+        <v>-133000</v>
       </c>
       <c r="H21" s="3">
-        <v>448400</v>
+        <v>136500</v>
       </c>
       <c r="I21" s="3">
-        <v>17800</v>
+        <v>436100</v>
       </c>
       <c r="J21" s="3">
+        <v>17300</v>
+      </c>
+      <c r="K21" s="3">
         <v>196600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>47200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1345400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>692900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1044000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2233000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>985100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>713300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-112800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-329100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-809100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-522300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-112000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>242200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>486500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>236900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>591800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>777500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>616300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>395300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>586700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>751200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>942400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-356700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>462600</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>207900</v>
+        <v>222100</v>
       </c>
       <c r="E22" s="3">
-        <v>197500</v>
+        <v>202200</v>
       </c>
       <c r="F22" s="3">
-        <v>185700</v>
+        <v>192100</v>
       </c>
       <c r="G22" s="3">
-        <v>172800</v>
+        <v>180600</v>
       </c>
       <c r="H22" s="3">
-        <v>194400</v>
+        <v>168100</v>
       </c>
       <c r="I22" s="3">
-        <v>164800</v>
+        <v>189100</v>
       </c>
       <c r="J22" s="3">
+        <v>160300</v>
+      </c>
+      <c r="K22" s="3">
         <v>165000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>172000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>137300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>165300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>163000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>114100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>170300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>137900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>151600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>153700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>157200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>109600</v>
       </c>
-      <c r="V22" s="3" t="s">
+      <c r="W22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>101700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>102100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>91800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>101900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>188500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>110300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>131700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>141600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>147200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>142400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>159500</v>
       </c>
-      <c r="AH22" s="3" t="s">
+      <c r="AI22" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-382600</v>
+        <v>-1082000</v>
       </c>
       <c r="E23" s="3">
-        <v>-337400</v>
+        <v>-372200</v>
       </c>
       <c r="F23" s="3">
-        <v>-559900</v>
+        <v>-328300</v>
       </c>
       <c r="G23" s="3">
-        <v>-273400</v>
+        <v>-544600</v>
       </c>
       <c r="H23" s="3">
-        <v>26600</v>
+        <v>-265900</v>
       </c>
       <c r="I23" s="3">
-        <v>-411400</v>
+        <v>25900</v>
       </c>
       <c r="J23" s="3">
+        <v>-400200</v>
+      </c>
+      <c r="K23" s="3">
         <v>-185800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-348300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1005600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>251900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>687900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1940300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>634400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>379600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-470600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-673800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1158100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-821100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-276500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-13400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>223100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>12800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>344000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>318600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>333200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>68800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>254200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>418900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>625800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-696900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>286200</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-125800</v>
+        <v>-379900</v>
       </c>
       <c r="E24" s="3">
-        <v>-13900</v>
+        <v>-122400</v>
       </c>
       <c r="F24" s="3">
-        <v>-87200</v>
+        <v>-13600</v>
       </c>
       <c r="G24" s="3">
-        <v>-121200</v>
+        <v>-84800</v>
       </c>
       <c r="H24" s="3">
-        <v>-18200</v>
+        <v>-117900</v>
       </c>
       <c r="I24" s="3">
-        <v>-63500</v>
+        <v>-17700</v>
       </c>
       <c r="J24" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="K24" s="3">
         <v>76900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-55200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>214500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>157400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-20500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>476000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>167100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>215400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-210100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-181900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-358300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-288200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-91400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-23600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>51500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>44600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>77100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>14500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>64500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-11400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>58400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>126000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>153200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-46600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>84600</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-256800</v>
+        <v>-702000</v>
       </c>
       <c r="E26" s="3">
-        <v>-323500</v>
+        <v>-249800</v>
       </c>
       <c r="F26" s="3">
-        <v>-472600</v>
+        <v>-314700</v>
       </c>
       <c r="G26" s="3">
-        <v>-152100</v>
+        <v>-459800</v>
       </c>
       <c r="H26" s="3">
-        <v>44800</v>
+        <v>-148000</v>
       </c>
       <c r="I26" s="3">
-        <v>-348000</v>
+        <v>43600</v>
       </c>
       <c r="J26" s="3">
+        <v>-338500</v>
+      </c>
+      <c r="K26" s="3">
         <v>-262700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-293200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>791100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>94500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>708500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1464200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>467400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>164200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-260500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-492000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-799900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-532900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-185000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>10200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>171600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-31900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>266800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>304100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>268800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>80200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>195800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>292900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>472700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-650200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>201700</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-248500</v>
+        <v>-671300</v>
       </c>
       <c r="E27" s="3">
-        <v>-290900</v>
+        <v>-241700</v>
       </c>
       <c r="F27" s="3">
-        <v>-446800</v>
+        <v>-283000</v>
       </c>
       <c r="G27" s="3">
-        <v>-142400</v>
+        <v>-434600</v>
       </c>
       <c r="H27" s="3">
-        <v>34100</v>
+        <v>-138500</v>
       </c>
       <c r="I27" s="3">
-        <v>-316000</v>
+        <v>33100</v>
       </c>
       <c r="J27" s="3">
+        <v>-307400</v>
+      </c>
+      <c r="K27" s="3">
         <v>-203800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-281800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>778400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>107000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>712300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1437400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>483000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>158300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-275200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-487900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-719100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-539700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-166500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>14900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>173700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>248700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>296200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>246000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>99000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>204900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>279400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>446200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-628800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>219400</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2754,16 +2815,19 @@
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>2200</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>900</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>167200</v>
+        <v>831600</v>
       </c>
       <c r="E32" s="3">
-        <v>-49900</v>
+        <v>162700</v>
       </c>
       <c r="F32" s="3">
-        <v>259600</v>
+        <v>-48600</v>
       </c>
       <c r="G32" s="3">
-        <v>-202500</v>
+        <v>252600</v>
       </c>
       <c r="H32" s="3">
-        <v>-129400</v>
+        <v>-197000</v>
       </c>
       <c r="I32" s="3">
-        <v>-93900</v>
+        <v>-125900</v>
       </c>
       <c r="J32" s="3">
+        <v>-91300</v>
+      </c>
+      <c r="K32" s="3">
         <v>148300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>508000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-387400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>334000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>462000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-299500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>500400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-305900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>205200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>324000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1075200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>51500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>381300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>61000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>70600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>102900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>70400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>297800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>365400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>99500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>26500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-46800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>229800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>283500</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-248500</v>
+        <v>-671300</v>
       </c>
       <c r="E33" s="3">
-        <v>-290900</v>
+        <v>-241700</v>
       </c>
       <c r="F33" s="3">
-        <v>-446800</v>
+        <v>-283000</v>
       </c>
       <c r="G33" s="3">
-        <v>-142400</v>
+        <v>-434600</v>
       </c>
       <c r="H33" s="3">
-        <v>34100</v>
+        <v>-138500</v>
       </c>
       <c r="I33" s="3">
-        <v>-316000</v>
+        <v>33100</v>
       </c>
       <c r="J33" s="3">
+        <v>-307400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-203800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-281800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>778400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>107000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>712300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1437400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>483000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>158300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-275200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-487900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-719100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-539700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-166500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>14900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>173700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>248700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>296200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>246000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>99000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>204900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>279400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>448400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-628000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>220700</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-248500</v>
+        <v>-671300</v>
       </c>
       <c r="E35" s="3">
-        <v>-290900</v>
+        <v>-241700</v>
       </c>
       <c r="F35" s="3">
-        <v>-446800</v>
+        <v>-283000</v>
       </c>
       <c r="G35" s="3">
-        <v>-142400</v>
+        <v>-434600</v>
       </c>
       <c r="H35" s="3">
-        <v>34100</v>
+        <v>-138500</v>
       </c>
       <c r="I35" s="3">
-        <v>-316000</v>
+        <v>33100</v>
       </c>
       <c r="J35" s="3">
+        <v>-307400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-203800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-281800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>778400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>107000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>712300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1437400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>483000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>158300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-275200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-487900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-719100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-539700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-166500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>14900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>173700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>248700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>296200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>246000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>99000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>204900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>279400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>448400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-628000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>220700</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,890 +3611,918 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2626400</v>
+        <v>2554500</v>
       </c>
       <c r="E41" s="3">
-        <v>2621200</v>
+        <v>2554900</v>
       </c>
       <c r="F41" s="3">
-        <v>2519500</v>
+        <v>2549800</v>
       </c>
       <c r="G41" s="3">
-        <v>2446300</v>
+        <v>2450900</v>
       </c>
       <c r="H41" s="3">
-        <v>2287900</v>
+        <v>2379700</v>
       </c>
       <c r="I41" s="3">
-        <v>2303300</v>
+        <v>2225600</v>
       </c>
       <c r="J41" s="3">
+        <v>2240600</v>
+      </c>
+      <c r="K41" s="3">
         <v>2168600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1909600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2027200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1752100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2422000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1890800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2419100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2593600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2400500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2953000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1981600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1256700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1072000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1024900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1142200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>989700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>905000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>952900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>797100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>967900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1397900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1464300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1641600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1662600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2034300</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>731600</v>
+        <v>560000</v>
       </c>
       <c r="E42" s="3">
-        <v>915700</v>
+        <v>711700</v>
       </c>
       <c r="F42" s="3">
-        <v>931600</v>
+        <v>890700</v>
       </c>
       <c r="G42" s="3">
-        <v>432400</v>
+        <v>906300</v>
       </c>
       <c r="H42" s="3">
-        <v>707300</v>
+        <v>420600</v>
       </c>
       <c r="I42" s="3">
-        <v>424100</v>
+        <v>688100</v>
       </c>
       <c r="J42" s="3">
+        <v>412600</v>
+      </c>
+      <c r="K42" s="3">
         <v>460400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>766700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>416000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>705000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>591300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>736800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>751000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>678600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>624200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>542500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>451600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>311700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>241600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>120300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>321900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>420600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>385000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>380400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>569800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>590400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>585700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>686500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>250900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>295300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>107400</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>957400</v>
+        <v>1006100</v>
       </c>
       <c r="E43" s="3">
-        <v>886700</v>
+        <v>931400</v>
       </c>
       <c r="F43" s="3">
-        <v>1100900</v>
+        <v>862500</v>
       </c>
       <c r="G43" s="3">
-        <v>1017100</v>
+        <v>1071000</v>
       </c>
       <c r="H43" s="3">
-        <v>1195500</v>
+        <v>989400</v>
       </c>
       <c r="I43" s="3">
-        <v>1017600</v>
+        <v>1162900</v>
       </c>
       <c r="J43" s="3">
+        <v>989900</v>
+      </c>
+      <c r="K43" s="3">
         <v>1687300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1889000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1979000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2082100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2738400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2403300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2135000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1485100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1319700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1157500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1084200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1321200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1026100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>893800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>861400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>842900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1091300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>836300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1029700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1263800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1077900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1019500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>752400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>658900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>796900</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2449200</v>
+        <v>2428500</v>
       </c>
       <c r="E44" s="3">
-        <v>2315400</v>
+        <v>2382500</v>
       </c>
       <c r="F44" s="3">
-        <v>2305100</v>
+        <v>2252400</v>
       </c>
       <c r="G44" s="3">
-        <v>2399000</v>
+        <v>2242300</v>
       </c>
       <c r="H44" s="3">
-        <v>2546300</v>
+        <v>2333700</v>
       </c>
       <c r="I44" s="3">
-        <v>2592200</v>
+        <v>2477000</v>
       </c>
       <c r="J44" s="3">
+        <v>2521600</v>
+      </c>
+      <c r="K44" s="3">
         <v>2773900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3411700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3396800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3297100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2893300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2460700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2311800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1568500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1571000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1452200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1543800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1408400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1476000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1464000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1515400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1514000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1655100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1501300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1559800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1755400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1473200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1514600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1375900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1299400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1209100</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>155200</v>
+        <v>251300</v>
       </c>
       <c r="E45" s="3">
-        <v>178700</v>
+        <v>151000</v>
       </c>
       <c r="F45" s="3">
-        <v>29900</v>
+        <v>173800</v>
       </c>
       <c r="G45" s="3">
-        <v>49800</v>
+        <v>29100</v>
       </c>
       <c r="H45" s="3">
-        <v>32000</v>
+        <v>48400</v>
       </c>
       <c r="I45" s="3">
-        <v>29200</v>
+        <v>31100</v>
       </c>
       <c r="J45" s="3">
+        <v>28400</v>
+      </c>
+      <c r="K45" s="3">
         <v>10400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>18500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>149300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>94700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>39100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>67600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>69200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>70800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>84700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>79500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>18600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>22100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>29700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>39900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>59800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>47700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>24700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>29100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>31200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>35400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>51200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>52400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>111400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>116600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>6919800</v>
+        <v>6800400</v>
       </c>
       <c r="E46" s="3">
-        <v>6917600</v>
+        <v>6731400</v>
       </c>
       <c r="F46" s="3">
-        <v>6887100</v>
+        <v>6729300</v>
       </c>
       <c r="G46" s="3">
-        <v>6344500</v>
+        <v>6699600</v>
       </c>
       <c r="H46" s="3">
-        <v>6769000</v>
+        <v>6171800</v>
       </c>
       <c r="I46" s="3">
-        <v>6366400</v>
+        <v>6584700</v>
       </c>
       <c r="J46" s="3">
+        <v>6193100</v>
+      </c>
+      <c r="K46" s="3">
         <v>7100500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7995400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7968300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7931000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8684100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7559200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7686000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6396700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6000200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6184600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5079800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4320100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3845500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3542900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3900600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3814900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4061100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3700000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3987600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4612900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4585900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4737400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4132100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4032900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4186700</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>389100</v>
+        <v>374400</v>
       </c>
       <c r="E47" s="3">
+        <v>378500</v>
+      </c>
+      <c r="F47" s="3">
+        <v>366100</v>
+      </c>
+      <c r="G47" s="3">
+        <v>419600</v>
+      </c>
+      <c r="H47" s="3">
+        <v>420600</v>
+      </c>
+      <c r="I47" s="3">
+        <v>418400</v>
+      </c>
+      <c r="J47" s="3">
+        <v>396700</v>
+      </c>
+      <c r="K47" s="3">
+        <v>435500</v>
+      </c>
+      <c r="L47" s="3">
+        <v>438300</v>
+      </c>
+      <c r="M47" s="3">
         <v>376400</v>
       </c>
-      <c r="F47" s="3">
-        <v>431300</v>
-      </c>
-      <c r="G47" s="3">
-        <v>432400</v>
-      </c>
-      <c r="H47" s="3">
-        <v>430100</v>
-      </c>
-      <c r="I47" s="3">
-        <v>407800</v>
-      </c>
-      <c r="J47" s="3">
-        <v>435500</v>
-      </c>
-      <c r="K47" s="3">
-        <v>438300</v>
-      </c>
-      <c r="L47" s="3">
-        <v>376400</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>391000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>360300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>444500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>291700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>272100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>454400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>516900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>628100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>511200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>441100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>506500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>562700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>338000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>238400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>250800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>309100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>329600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>378500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>380000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>362800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>345300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>426900</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>7844400</v>
+        <v>7784100</v>
       </c>
       <c r="E48" s="3">
-        <v>7801500</v>
+        <v>7630800</v>
       </c>
       <c r="F48" s="3">
-        <v>7781800</v>
+        <v>7589100</v>
       </c>
       <c r="G48" s="3">
-        <v>7684300</v>
+        <v>7570000</v>
       </c>
       <c r="H48" s="3">
-        <v>7783100</v>
+        <v>7475100</v>
       </c>
       <c r="I48" s="3">
-        <v>7707500</v>
+        <v>7571200</v>
       </c>
       <c r="J48" s="3">
+        <v>7497700</v>
+      </c>
+      <c r="K48" s="3">
         <v>7596100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7898100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7344600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8074600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7859700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7278100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7805500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7265000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7612900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7485700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7310600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6449900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6356800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5860000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6264500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5666000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6059100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5851700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7088700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7630300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7640900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7806300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7344800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>7277900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>7403700</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>576300</v>
+        <v>584100</v>
       </c>
       <c r="E49" s="3">
-        <v>574200</v>
+        <v>560600</v>
       </c>
       <c r="F49" s="3">
-        <v>574100</v>
+        <v>558600</v>
       </c>
       <c r="G49" s="3">
-        <v>568800</v>
+        <v>558400</v>
       </c>
       <c r="H49" s="3">
+        <v>553300</v>
+      </c>
+      <c r="I49" s="3">
+        <v>554300</v>
+      </c>
+      <c r="J49" s="3">
+        <v>543200</v>
+      </c>
+      <c r="K49" s="3">
+        <v>543900</v>
+      </c>
+      <c r="L49" s="3">
+        <v>571400</v>
+      </c>
+      <c r="M49" s="3">
+        <v>565400</v>
+      </c>
+      <c r="N49" s="3">
+        <v>580800</v>
+      </c>
+      <c r="O49" s="3">
         <v>569800</v>
       </c>
-      <c r="I49" s="3">
-        <v>558400</v>
-      </c>
-      <c r="J49" s="3">
-        <v>543900</v>
-      </c>
-      <c r="K49" s="3">
-        <v>571400</v>
-      </c>
-      <c r="L49" s="3">
-        <v>565400</v>
-      </c>
-      <c r="M49" s="3">
-        <v>580800</v>
-      </c>
-      <c r="N49" s="3">
-        <v>569800</v>
-      </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>543300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>550000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>529200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>547400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>548300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>546700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>510200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>515400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>483000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>510800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>489000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>508500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>506900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>633500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>699300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>704400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>714300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>689900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>696900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>699100</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1553300</v>
+        <v>1901700</v>
       </c>
       <c r="E52" s="3">
-        <v>1280400</v>
+        <v>1511000</v>
       </c>
       <c r="F52" s="3">
-        <v>1326400</v>
+        <v>1245500</v>
       </c>
       <c r="G52" s="3">
-        <v>1230600</v>
+        <v>1290300</v>
       </c>
       <c r="H52" s="3">
-        <v>1159400</v>
+        <v>1197100</v>
       </c>
       <c r="I52" s="3">
-        <v>1227800</v>
+        <v>1127900</v>
       </c>
       <c r="J52" s="3">
+        <v>1194400</v>
+      </c>
+      <c r="K52" s="3">
         <v>1360500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1489300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1168100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1705900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1545100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1201600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1881700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1642500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2165100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1926900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1643300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>792100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1120900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>905000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>258100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>252400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>381100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>451100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>313100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>403600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>326100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>353300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>386600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>503100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>457300</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>17282800</v>
+        <v>17444800</v>
       </c>
       <c r="E54" s="3">
-        <v>16950100</v>
+        <v>16812300</v>
       </c>
       <c r="F54" s="3">
-        <v>17000800</v>
+        <v>16488600</v>
       </c>
       <c r="G54" s="3">
-        <v>16260600</v>
+        <v>16537900</v>
       </c>
       <c r="H54" s="3">
-        <v>16711400</v>
+        <v>15817900</v>
       </c>
       <c r="I54" s="3">
-        <v>16267900</v>
+        <v>16256500</v>
       </c>
       <c r="J54" s="3">
+        <v>15825000</v>
+      </c>
+      <c r="K54" s="3">
         <v>17036500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>18392400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17422800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18683200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>19019100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17026700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>18214800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16105400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16780100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16662500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>15208500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>12583400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>12279700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>11297500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>11496800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>10560200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>11248200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10760600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12332000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>13675700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>13635900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>13991200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12916200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12856000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>13173700</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2752700</v>
+        <v>2979700</v>
       </c>
       <c r="E57" s="3">
-        <v>2442700</v>
+        <v>2677800</v>
       </c>
       <c r="F57" s="3">
-        <v>2453200</v>
+        <v>2376200</v>
       </c>
       <c r="G57" s="3">
-        <v>2210300</v>
+        <v>2386400</v>
       </c>
       <c r="H57" s="3">
-        <v>2262100</v>
+        <v>2150200</v>
       </c>
       <c r="I57" s="3">
-        <v>2262700</v>
+        <v>2200500</v>
       </c>
       <c r="J57" s="3">
+        <v>2201100</v>
+      </c>
+      <c r="K57" s="3">
         <v>2375900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2547700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2415800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2432800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2102200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2067800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2653800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1860900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1727400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1688200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1944600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1683900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1707000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1614000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1543200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1488100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1736200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1528000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1323600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1350000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1233400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1348000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1257900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1623700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1777600</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>584200</v>
+        <v>694700</v>
       </c>
       <c r="E58" s="3">
-        <v>692100</v>
+        <v>568300</v>
       </c>
       <c r="F58" s="3">
-        <v>621300</v>
+        <v>673300</v>
       </c>
       <c r="G58" s="3">
-        <v>647700</v>
+        <v>604400</v>
       </c>
       <c r="H58" s="3">
-        <v>616800</v>
+        <v>630000</v>
       </c>
       <c r="I58" s="3">
-        <v>608000</v>
+        <v>600000</v>
       </c>
       <c r="J58" s="3">
+        <v>591400</v>
+      </c>
+      <c r="K58" s="3">
         <v>468100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>533800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>614800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>436900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1812300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1976400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2022700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1857500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>672200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1099500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>786300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>414200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2599500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2298100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2118700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2010500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2235800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2243600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2379100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2795400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3374100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3695000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3205900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3233000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>731800</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1458100</v>
+        <v>1512400</v>
       </c>
       <c r="E59" s="3">
-        <v>1390700</v>
+        <v>1418400</v>
       </c>
       <c r="F59" s="3">
-        <v>1393000</v>
+        <v>1352800</v>
       </c>
       <c r="G59" s="3">
-        <v>1412200</v>
+        <v>1355100</v>
       </c>
       <c r="H59" s="3">
-        <v>1566000</v>
+        <v>1373700</v>
       </c>
       <c r="I59" s="3">
-        <v>1597800</v>
+        <v>1523400</v>
       </c>
       <c r="J59" s="3">
+        <v>1554300</v>
+      </c>
+      <c r="K59" s="3">
         <v>1791900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2068000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1853600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2215300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2603500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1966700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1796200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1592600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1664100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1451600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1196900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>897100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>679000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>571900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>546700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>625300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>522000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>498700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>526100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>761100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>719900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>760100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>881200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>858600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>814100</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4795100</v>
+        <v>5186800</v>
       </c>
       <c r="E60" s="3">
-        <v>4525500</v>
+        <v>4664500</v>
       </c>
       <c r="F60" s="3">
-        <v>4467500</v>
+        <v>4402300</v>
       </c>
       <c r="G60" s="3">
-        <v>4270200</v>
+        <v>4345900</v>
       </c>
       <c r="H60" s="3">
-        <v>4444800</v>
+        <v>4154000</v>
       </c>
       <c r="I60" s="3">
-        <v>4468500</v>
+        <v>4323800</v>
       </c>
       <c r="J60" s="3">
+        <v>4346800</v>
+      </c>
+      <c r="K60" s="3">
         <v>4635900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5149500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4884200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5085100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6518000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6010900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6472700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5311000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4063700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4239400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3927700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2995100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4985500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4483900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4208600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4123900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4494000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4270300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4228800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4906500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5327400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5803000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5344900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5715300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3323500</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10201500</v>
+        <v>10782400</v>
       </c>
       <c r="E61" s="3">
-        <v>9916600</v>
+        <v>9923800</v>
       </c>
       <c r="F61" s="3">
-        <v>9992400</v>
+        <v>9646600</v>
       </c>
       <c r="G61" s="3">
-        <v>8910900</v>
+        <v>9720300</v>
       </c>
       <c r="H61" s="3">
-        <v>9311400</v>
+        <v>8668300</v>
       </c>
       <c r="I61" s="3">
-        <v>8875300</v>
+        <v>9057900</v>
       </c>
       <c r="J61" s="3">
+        <v>8633700</v>
+      </c>
+      <c r="K61" s="3">
         <v>9126600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9348200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8260900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9768500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7992100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7319500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9345600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8850600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11502700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>11478900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>10039400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7334000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4956900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4362300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4937800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4310300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4438500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4496800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4981500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5685600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4740400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4970200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4871100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5144300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7597500</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1848700</v>
+        <v>1649200</v>
       </c>
       <c r="E62" s="3">
-        <v>1902100</v>
+        <v>1798400</v>
       </c>
       <c r="F62" s="3">
-        <v>1732000</v>
+        <v>1850300</v>
       </c>
       <c r="G62" s="3">
-        <v>1833700</v>
+        <v>1684800</v>
       </c>
       <c r="H62" s="3">
-        <v>1633700</v>
+        <v>1783700</v>
       </c>
       <c r="I62" s="3">
-        <v>1795600</v>
+        <v>1589200</v>
       </c>
       <c r="J62" s="3">
+        <v>1746700</v>
+      </c>
+      <c r="K62" s="3">
         <v>2012300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2293800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2215500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2577400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2266500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2308600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2685000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2667200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2462700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1996200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1806400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1525700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1173400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1112200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1004100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1071500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1129300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1096400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1408600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1624600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1772800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1746400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1575400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1569400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1162700</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>16713200</v>
+        <v>17429500</v>
       </c>
       <c r="E66" s="3">
-        <v>16212500</v>
+        <v>16258200</v>
       </c>
       <c r="F66" s="3">
-        <v>16072800</v>
+        <v>15771100</v>
       </c>
       <c r="G66" s="3">
-        <v>14924300</v>
+        <v>15635200</v>
       </c>
       <c r="H66" s="3">
-        <v>15265400</v>
+        <v>14518000</v>
       </c>
       <c r="I66" s="3">
-        <v>14915100</v>
+        <v>14849800</v>
       </c>
       <c r="J66" s="3">
+        <v>14509100</v>
+      </c>
+      <c r="K66" s="3">
         <v>15431100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16494600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15098200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>17095600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16448400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15349800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18131500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16517500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>17649700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>17328600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15405600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11681100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10917200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9805200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9987100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9349300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9920900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>9696800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>10466600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>12004700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>11654000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>12338600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>11595600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>12176600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>11845300</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-754000</v>
+        <v>-1404400</v>
       </c>
       <c r="E72" s="3">
-        <v>-505900</v>
+        <v>-733500</v>
       </c>
       <c r="F72" s="3">
-        <v>-215500</v>
+        <v>-492100</v>
       </c>
       <c r="G72" s="3">
-        <v>230800</v>
+        <v>-209700</v>
       </c>
       <c r="H72" s="3">
-        <v>373800</v>
+        <v>224500</v>
       </c>
       <c r="I72" s="3">
-        <v>338400</v>
+        <v>363600</v>
       </c>
       <c r="J72" s="3">
+        <v>329200</v>
+      </c>
+      <c r="K72" s="3">
         <v>653100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>928100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1478700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>703900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1802600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1046900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-392800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-847400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1047900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-783000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-296500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>394800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>947600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1050500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1111600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>875200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1044400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>794400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1223400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1071200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1226800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1020100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>714900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>264700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>914200</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>569600</v>
+        <v>15300</v>
       </c>
       <c r="E76" s="3">
-        <v>737600</v>
+        <v>554100</v>
       </c>
       <c r="F76" s="3">
-        <v>928000</v>
+        <v>717500</v>
       </c>
       <c r="G76" s="3">
-        <v>1336300</v>
+        <v>902700</v>
       </c>
       <c r="H76" s="3">
-        <v>1446100</v>
+        <v>1299900</v>
       </c>
       <c r="I76" s="3">
-        <v>1352800</v>
+        <v>1406700</v>
       </c>
       <c r="J76" s="3">
+        <v>1315900</v>
+      </c>
+      <c r="K76" s="3">
         <v>1605400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1897800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2324600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1587600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2570700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1676800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>83300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-412000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-869600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-666100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-197100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>902300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1362500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1492300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1509600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1210900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1327200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1063800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1865400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1671000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1981900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1652600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1320600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>679400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1328400</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-248500</v>
+        <v>-671300</v>
       </c>
       <c r="E81" s="3">
-        <v>-290900</v>
+        <v>-241700</v>
       </c>
       <c r="F81" s="3">
-        <v>-446800</v>
+        <v>-283000</v>
       </c>
       <c r="G81" s="3">
-        <v>-142400</v>
+        <v>-434600</v>
       </c>
       <c r="H81" s="3">
-        <v>34100</v>
+        <v>-138500</v>
       </c>
       <c r="I81" s="3">
-        <v>-316000</v>
+        <v>33100</v>
       </c>
       <c r="J81" s="3">
+        <v>-307400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-203800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-281800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>778400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>107000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>712300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1437400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>483000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>158300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-275200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-487900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-719100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-539700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-166500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>14900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>173700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-14000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>248700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>296200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>246000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>99000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>204900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>279400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>448400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-628000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>220700</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>227100</v>
+        <v>231500</v>
       </c>
       <c r="E83" s="3">
-        <v>256100</v>
+        <v>220900</v>
       </c>
       <c r="F83" s="3">
-        <v>237500</v>
+        <v>249100</v>
       </c>
       <c r="G83" s="3">
-        <v>240900</v>
+        <v>231000</v>
       </c>
       <c r="H83" s="3">
-        <v>227300</v>
+        <v>234400</v>
       </c>
       <c r="I83" s="3">
-        <v>264400</v>
+        <v>221100</v>
       </c>
       <c r="J83" s="3">
+        <v>257200</v>
+      </c>
+      <c r="K83" s="3">
         <v>217300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>223600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>202400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>275600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>193100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>178600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>180400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>195800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>206200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>191000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>191800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>189200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>164500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>153900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>161300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>132300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>145800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>270300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>172800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>194800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>191000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>185100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>174200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>177700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>176400</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>178300</v>
+        <v>259500</v>
       </c>
       <c r="E89" s="3">
-        <v>187300</v>
+        <v>173400</v>
       </c>
       <c r="F89" s="3">
-        <v>-455200</v>
+        <v>182200</v>
       </c>
       <c r="G89" s="3">
-        <v>365700</v>
+        <v>-442800</v>
       </c>
       <c r="H89" s="3">
-        <v>-517700</v>
+        <v>355800</v>
       </c>
       <c r="I89" s="3">
-        <v>426900</v>
+        <v>-503600</v>
       </c>
       <c r="J89" s="3">
+        <v>415300</v>
+      </c>
+      <c r="K89" s="3">
         <v>542400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>400000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>342600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>854400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1155500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>486500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>446100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>718300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>189200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-129900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>422000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>169400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>150400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-88200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>195400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>179800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>391200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1133900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>420500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>341000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>377300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-232900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>141000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>179800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>704800</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1888000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1233000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1224500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-908300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1164300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1531300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1509900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1108600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-698500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1378400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-819300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-142000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-94900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-155100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-88700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-112300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-178400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-164900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-118100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-124700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-85300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-160800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-122100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-211900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-94500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-187200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-198300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-120300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-67700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-418100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-262200</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-160900</v>
+        <v>-172900</v>
       </c>
       <c r="E94" s="3">
-        <v>-278600</v>
+        <v>-156500</v>
       </c>
       <c r="F94" s="3">
-        <v>-226100</v>
+        <v>-271000</v>
       </c>
       <c r="G94" s="3">
-        <v>-160500</v>
+        <v>-219900</v>
       </c>
       <c r="H94" s="3">
-        <v>-170900</v>
+        <v>-156100</v>
       </c>
       <c r="I94" s="3">
-        <v>-283900</v>
+        <v>-166200</v>
       </c>
       <c r="J94" s="3">
+        <v>-276200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-286600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-230000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-142700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-278000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-165000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-137300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-92000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-151100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-88700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-109600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-177800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-162900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-169800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-75000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-85300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-150800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-107300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-196700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-94200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-341100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-195500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-9900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-68200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-206800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-130100</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8361,17 +8595,17 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>-100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-500</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -8379,20 +8613,20 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-270600</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-1209300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-400</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -8403,23 +8637,23 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-500</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-123100</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-400</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -8427,17 +8661,17 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-277500</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-256100</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
@@ -8445,13 +8679,16 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-247800</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-48800</v>
+        <v>-183900</v>
       </c>
       <c r="E100" s="3">
-        <v>214100</v>
+        <v>-47400</v>
       </c>
       <c r="F100" s="3">
-        <v>727200</v>
+        <v>208200</v>
       </c>
       <c r="G100" s="3">
-        <v>11400</v>
+        <v>707400</v>
       </c>
       <c r="H100" s="3">
-        <v>686700</v>
+        <v>11100</v>
       </c>
       <c r="I100" s="3">
-        <v>26900</v>
+        <v>668000</v>
       </c>
       <c r="J100" s="3">
+        <v>26200</v>
+      </c>
+      <c r="K100" s="3">
         <v>118900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-377700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>264700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1291300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-606100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-757400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-706100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-217000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-646300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1126300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>184400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>212200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-24900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>123000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-13900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>73500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-297900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-630100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-405100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-416900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-275700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>35200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-105200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-237800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-197800</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>36600</v>
+        <v>96900</v>
       </c>
       <c r="E101" s="3">
-        <v>-21100</v>
+        <v>35600</v>
       </c>
       <c r="F101" s="3">
-        <v>27300</v>
+        <v>-20500</v>
       </c>
       <c r="G101" s="3">
-        <v>-58300</v>
+        <v>26600</v>
       </c>
       <c r="H101" s="3">
-        <v>-13500</v>
+        <v>-56700</v>
       </c>
       <c r="I101" s="3">
-        <v>-35200</v>
+        <v>-13200</v>
       </c>
       <c r="J101" s="3">
+        <v>-34200</v>
+      </c>
+      <c r="K101" s="3">
         <v>33600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>90000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-177200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>39700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>71000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-120100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>86800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-62400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>27600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>84600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>212200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-17600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>30500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-15700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>7900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>14500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-33800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-52700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-5700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-13000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>27500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-24500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>11300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>14900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-10500</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>5200</v>
+        <v>-400</v>
       </c>
       <c r="E102" s="3">
-        <v>101700</v>
+        <v>5000</v>
       </c>
       <c r="F102" s="3">
-        <v>73300</v>
+        <v>99000</v>
       </c>
       <c r="G102" s="3">
-        <v>158300</v>
+        <v>71300</v>
       </c>
       <c r="H102" s="3">
-        <v>-15400</v>
+        <v>154000</v>
       </c>
       <c r="I102" s="3">
-        <v>134700</v>
+        <v>-15000</v>
       </c>
       <c r="J102" s="3">
+        <v>131100</v>
+      </c>
+      <c r="K102" s="3">
         <v>408200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-117600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>287400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-675200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>455300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-528300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-265200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>287800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-518300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>971300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>640800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>201100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-13700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-55900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>104100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>117100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-47900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>254400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-84500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-430000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-66400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-232200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-21000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-254500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>362100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BAK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
   <si>
     <t>BAK</t>
   </si>
@@ -656,149 +656,174 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2968900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2923200</v>
+      </c>
+      <c r="F8" s="3">
         <v>3246000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>3277200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>3394100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>3096600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3905100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>3435900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>3572900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3439800</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2758100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2690800</v>
+      </c>
+      <c r="F9" s="3">
         <v>3164100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3210800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3165600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2911100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3492100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3185600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3331500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>3232100</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>210900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>232400</v>
+      </c>
+      <c r="F10" s="3">
         <v>81800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>66400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>228500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>185500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>413000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>250400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>241500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>207700</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -810,37 +835,45 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>19100</v>
+      </c>
+      <c r="F12" s="3">
         <v>22700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>19800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>22000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>23000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>20000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>19100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>21100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -868,66 +901,84 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>389600</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-3700</v>
       </c>
-      <c r="F14" s="3">
-        <v>3100</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="I14" s="3">
+        <v>22600</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="K14" s="3">
+        <v>4900</v>
+      </c>
+      <c r="L14" s="3">
+        <v>3800</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="3">
-        <v>4900</v>
-      </c>
-      <c r="J14" s="3">
-        <v>3800</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>183100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>163400</v>
+      </c>
+      <c r="F15" s="3">
         <v>158200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>184600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>163400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>135200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>184400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>177100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>185600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>173500</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -936,66 +987,80 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2999600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2485700</v>
+      </c>
+      <c r="F17" s="3">
         <v>3559300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3375600</v>
       </c>
-      <c r="F17" s="3">
-        <v>3372500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>3403300</v>
-      </c>
       <c r="H17" s="3">
+        <v>3381400</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3380700</v>
+      </c>
+      <c r="J17" s="3">
         <v>3719600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3455400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3576300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3651500</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>437500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-313400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-98400</v>
       </c>
-      <c r="F18" s="3">
-        <v>21600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-306700</v>
-      </c>
       <c r="H18" s="3">
+        <v>12700</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-284100</v>
+      </c>
+      <c r="J18" s="3">
         <v>185500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-19500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-211700</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1007,153 +1072,185 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-465200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-101300</v>
+      </c>
+      <c r="F20" s="3">
         <v>-55200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-177800</v>
       </c>
-      <c r="F20" s="3">
-        <v>-305000</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>-313100</v>
+      </c>
+      <c r="I20" s="3">
         <v>772500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>216000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>908000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>252800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>617600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>702300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-100000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>264100</v>
       </c>
-      <c r="F21" s="3">
-        <v>490100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-944100</v>
-      </c>
       <c r="H21" s="3">
+        <v>489200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-921400</v>
+      </c>
+      <c r="J21" s="3">
         <v>153900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-750400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-70600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-47600</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>255900</v>
+      </c>
+      <c r="E22" s="3">
+        <v>273200</v>
+      </c>
+      <c r="F22" s="3">
         <v>300000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>216700</v>
       </c>
-      <c r="F22" s="3">
-        <v>217800</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
+        <v>225900</v>
+      </c>
+      <c r="I22" s="3">
         <v>309600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>291300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>211500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>224300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>259300</v>
       </c>
     </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>182700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-98000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-486200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-97300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>142300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1346700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-241100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1084400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-412900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-376300</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-56200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1904300</v>
+      </c>
+      <c r="F24" s="3">
         <v>-453500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-25700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>32100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-394800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-81500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-380800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-135800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-15500</v>
       </c>
     </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1181,66 +1278,84 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>238800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2002400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-32600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-71600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>110200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-951800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-159600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-703600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-277100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-360900</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>277200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1867300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-4900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-49000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>121700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-913000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-108900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-672800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-268200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-324600</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1268,8 +1383,14 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1297,8 +1418,14 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1326,8 +1453,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1355,66 +1488,84 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>465200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>101300</v>
+      </c>
+      <c r="F32" s="3">
         <v>55200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>177800</v>
       </c>
-      <c r="F32" s="3">
-        <v>305000</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>313100</v>
+      </c>
+      <c r="I32" s="3">
         <v>-772500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-216000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-908000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-252800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-9500</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>277200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1867300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-4900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-49000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>121700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-913000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-108900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-672800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-268200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-324600</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1442,71 +1593,89 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>277200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1867300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-4900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-49000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>121700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-913000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-108900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-672800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-268200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-324600</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1518,8 +1687,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1531,269 +1702,325 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>896700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1906500</v>
+      </c>
+      <c r="F41" s="3">
         <v>1250200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1685300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1973800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2423000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2188900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2560200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2834200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2923800</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>262200</v>
+      </c>
+      <c r="E42" s="3">
+        <v>242600</v>
+      </c>
+      <c r="F42" s="3">
         <v>139800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>205700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>298600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>288800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>444100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>561300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>789600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>1021400</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1315200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1208100</v>
+      </c>
+      <c r="F43" s="3">
         <v>965600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1082600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>983900</v>
       </c>
-      <c r="G43" s="3">
-        <v>1051600</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>924200</v>
+      </c>
+      <c r="J43" s="3">
         <v>958100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1112800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1177200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1160100</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2160900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1892000</v>
+      </c>
+      <c r="F44" s="3">
         <v>2373400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2476900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2513600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2213100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>2561500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>2417000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2643000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>2582700</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>385500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>278900</v>
+      </c>
+      <c r="F45" s="3">
         <v>200800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>191600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>177700</v>
       </c>
-      <c r="G45" s="3">
-        <v>11800</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
+        <v>139200</v>
+      </c>
+      <c r="J45" s="3">
         <v>140300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>147300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>149700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>28200</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5020600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5528000</v>
+      </c>
+      <c r="F46" s="3">
         <v>4929800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5642200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5947700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>5988300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>6292900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>6798600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>7593700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>7716100</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>104300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>95000</v>
+      </c>
+      <c r="F47" s="3">
         <v>103800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>102400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>87600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>78300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>116400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>29500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>34300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>37700</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7590400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>7527800</v>
+      </c>
+      <c r="F48" s="3">
         <v>7805200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>7709200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>7376500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>7136100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>7626500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>7801400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>8465200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>8702100</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>575500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>556100</v>
+      </c>
+      <c r="F49" s="3">
         <v>569500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>588800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>578500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>547600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>586200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>585400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>621900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>640500</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1821,8 +2048,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1850,37 +2083,49 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>926800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>876000</v>
+      </c>
+      <c r="F52" s="3">
         <v>503100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>586700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>476300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>428300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>489400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>437900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>482100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>482500</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1908,37 +2153,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14543600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>14865500</v>
+      </c>
+      <c r="F54" s="3">
         <v>16396400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>16756500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>16642900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>16423100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>17015000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>17501600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>18650600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>18906700</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1950,8 +2207,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1963,182 +2222,220 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2156700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2392300</v>
+      </c>
+      <c r="F57" s="3">
         <v>2602900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2874600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2766400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2729700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2852600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2986300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2970600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2724700</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3954600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3935000</v>
+      </c>
+      <c r="F58" s="3">
         <v>551300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>684900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>606600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>668600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>641300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>696200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>630400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>772000</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>665600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>741100</v>
+      </c>
+      <c r="F59" s="3">
         <v>768900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>889000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>917200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>904800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1157500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1307400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1321500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1300800</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7075100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7301700</v>
+      </c>
+      <c r="F60" s="3">
         <v>4194100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4674600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4517500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4571100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4913300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>5209100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5211200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>5047900</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9012900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>9012700</v>
+      </c>
+      <c r="F61" s="3">
         <v>11314400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>11312200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>11423700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>11251100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>11239600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>11351500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>11536400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>11574500</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1200200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1188500</v>
+      </c>
+      <c r="F62" s="3">
         <v>1188900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1072300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1063200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>992100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>813000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>865300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>957600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1146100</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2166,8 +2463,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2195,8 +2498,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2224,37 +2533,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17655300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>17861500</v>
+      </c>
+      <c r="F66" s="3">
         <v>16991800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>17354500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>17304800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>17114700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>17289200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>17743900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>18178400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>18230900</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2266,8 +2587,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2295,8 +2618,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2324,8 +2653,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2353,8 +2688,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2382,37 +2723,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-4304600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-4339500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-2555800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-2495400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-2325500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-2269100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-1543200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-1475800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-813700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-564300</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2440,8 +2793,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2469,8 +2828,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2498,37 +2863,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-3016500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-2931600</v>
+      </c>
+      <c r="F76" s="3">
         <v>-662900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-698300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-738800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-773200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-4600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-53000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>614700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>822700</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2556,71 +2933,89 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>277200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1867300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-4900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-49000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>121700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-913000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-108900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-672800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-268200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-324600</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2632,37 +3027,45 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>202700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>178700</v>
+      </c>
+      <c r="F83" s="3">
         <v>231900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>227000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>239900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>279900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>240500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>274600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>237400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>249300</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2690,8 +3093,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2719,8 +3128,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2748,8 +3163,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2777,8 +3198,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2806,37 +3233,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-814500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-163400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-128200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-52300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-406700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>131900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-145100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>260100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>192400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>208800</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2848,37 +3287,45 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-125600</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-237900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-118900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-113900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-167000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-154100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-183600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-173500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-254100</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2906,8 +3353,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2935,37 +3388,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-176400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-112200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-198300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-127700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-100500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-164400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-115500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-174400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-173700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-245700</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2977,8 +3442,10 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -2991,23 +3458,29 @@
       <c r="F96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>900</v>
       </c>
-      <c r="J96" s="3" t="s">
+      <c r="L96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3035,8 +3508,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3064,8 +3543,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3093,91 +3578,115 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-69600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>932600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-137400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-190700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-33300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>385900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-117000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-183200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-52600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>173700</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-99400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>142400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-43700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>97100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>39500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-23500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>29600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-65500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-14400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-36100</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1116200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>696800</v>
+      </c>
+      <c r="F102" s="3">
         <v>-472800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-391600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-639900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>495900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-421300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>5600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>113300</v>
       </c>
     </row>
